--- a/reports/daily_report_13072026.xlsx
+++ b/reports/daily_report_13072026.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy hh:mm"/>
-    <numFmt numFmtId="166" formatCode="[h]:mm"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy hh:mm"/>
+    <numFmt numFmtId="165" formatCode="[h]:mm"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -59,11 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -523,10 +524,10 @@
           <t>Service interruption of 9 (2G)(4G) xC sites at certain parts of Sandakan - Telupid, Semporna area, Sabah</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>46216.88402777778</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="5">
         <f>IF(AND(E2&lt;&gt;"",F2&lt;&gt;""),F2-E2,"")</f>
         <v/>
       </c>
@@ -562,10 +563,10 @@
           <t>Service interruption of 9 (2G)(4G) xC sites at certain parts of Sandakan - Telupid, Semporna area, Sabah</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>46216.88402777778</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="5">
         <f>IF(AND(E3&lt;&gt;"",F3&lt;&gt;""),F3-E3,"")</f>
         <v/>
       </c>
@@ -601,10 +602,10 @@
           <t>Service interruption of 9 (2G)(4G) xC sites at certain parts of Sandakan - Telupid, Semporna area, Sabah</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="4" t="n">
         <v>46216.88402777778</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="5">
         <f>IF(AND(E4&lt;&gt;"",F4&lt;&gt;""),F4-E4,"")</f>
         <v/>
       </c>
@@ -640,10 +641,10 @@
           <t>Service interruption of 9 (2G)(4G) xC sites at certain parts of Sandakan - Telupid, Semporna area, Sabah</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="4" t="n">
         <v>46216.88402777778</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="5">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),F5-E5,"")</f>
         <v/>
       </c>
@@ -679,10 +680,10 @@
           <t>Service interruption of 9 (2G)(4G) xC sites at certain parts of Sandakan - Telupid, Semporna area, Sabah</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="4" t="n">
         <v>46216.88402777778</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="5">
         <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),F6-E6,"")</f>
         <v/>
       </c>
@@ -718,10 +719,10 @@
           <t>Service interruption of 9 (2G)(4G) xC sites at certain parts of Sandakan - Telupid, Semporna area, Sabah</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="4" t="n">
         <v>46216.88402777778</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="5">
         <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),F7-E7,"")</f>
         <v/>
       </c>
@@ -757,10 +758,10 @@
           <t>Service interruption of 9 (2G)(4G) xC sites at certain parts of Sandakan - Telupid, Semporna area, Sabah</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="4" t="n">
         <v>46216.88402777778</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="5">
         <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),F8-E8,"")</f>
         <v/>
       </c>
@@ -796,10 +797,10 @@
           <t>Service interruption of 9 (2G)(4G) xC sites at certain parts of Sandakan - Telupid, Semporna area, Sabah</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="4" t="n">
         <v>46216.88402777778</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="5">
         <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),F9-E9,"")</f>
         <v/>
       </c>
@@ -835,10 +836,10 @@
           <t>Service interruption of 9 (2G)(4G) xC sites at certain parts of Sandakan - Telupid, Semporna area, Sabah</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="4" t="n">
         <v>46216.88402777778</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="5">
         <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),F10-E10,"")</f>
         <v/>
       </c>
@@ -874,13 +875,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="5">
         <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),F11-E11,"")</f>
         <v/>
       </c>
@@ -926,13 +927,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="5">
         <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),F12-E12,"")</f>
         <v/>
       </c>
@@ -978,13 +979,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="5">
         <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),F13-E13,"")</f>
         <v/>
       </c>
@@ -1030,13 +1031,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="5">
         <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),F14-E14,"")</f>
         <v/>
       </c>
@@ -1082,13 +1083,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="5">
         <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),F15-E15,"")</f>
         <v/>
       </c>
@@ -1134,13 +1135,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="5">
         <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),F16-E16,"")</f>
         <v/>
       </c>
@@ -1186,13 +1187,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="5">
         <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),F17-E17,"")</f>
         <v/>
       </c>
@@ -1238,13 +1239,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="5">
         <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),F18-E18,"")</f>
         <v/>
       </c>
@@ -1290,13 +1291,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F19" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="5">
         <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),F19-E19,"")</f>
         <v/>
       </c>
@@ -1342,13 +1343,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F20" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="5">
         <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),F20-E20,"")</f>
         <v/>
       </c>
@@ -1394,13 +1395,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F21" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="5">
         <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),F21-E21,"")</f>
         <v/>
       </c>
@@ -1446,13 +1447,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F22" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="5">
         <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),F22-E22,"")</f>
         <v/>
       </c>
@@ -1498,13 +1499,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="5">
         <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),F23-E23,"")</f>
         <v/>
       </c>
@@ -1550,13 +1551,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F24" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="5">
         <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),F24-E24,"")</f>
         <v/>
       </c>
@@ -1602,13 +1603,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="5">
         <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),F25-E25,"")</f>
         <v/>
       </c>
@@ -1654,13 +1655,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F26" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="5">
         <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),F26-E26,"")</f>
         <v/>
       </c>
@@ -1706,13 +1707,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="F27" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="5">
         <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),F27-E27,"")</f>
         <v/>
       </c>
@@ -1758,13 +1759,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F28" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="5">
         <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),F28-E28,"")</f>
         <v/>
       </c>
@@ -1810,13 +1811,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F29" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="5">
         <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),F29-E29,"")</f>
         <v/>
       </c>
@@ -1862,13 +1863,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F30" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="5">
         <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),F30-E30,"")</f>
         <v/>
       </c>
@@ -1914,13 +1915,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E31" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F31" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="5">
         <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),F31-E31,"")</f>
         <v/>
       </c>
@@ -1966,13 +1967,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F32" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="5">
         <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),F32-E32,"")</f>
         <v/>
       </c>
@@ -2018,13 +2019,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E33" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="F33" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="5">
         <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),F33-E33,"")</f>
         <v/>
       </c>
@@ -2070,13 +2071,13 @@
           <t>Service interruption of 18 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Serian 1, Kota Samarahan / Asajaya area, Sarawak</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E34" s="4" t="n">
         <v>46216.84166666667</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F34" s="4" t="n">
         <v>46216.86875</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="5">
         <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),F34-E34,"")</f>
         <v/>
       </c>
@@ -2122,10 +2123,10 @@
           <t>Service interruption of 5 (2G)(4G) xD sites at certain parts of Kinabatangan, Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E35" s="4" t="n">
         <v>46216.72708333333</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="5">
         <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),F35-E35,"")</f>
         <v/>
       </c>
@@ -2161,10 +2162,10 @@
           <t>Service interruption of 5 (2G)(4G) xD sites at certain parts of Kinabatangan, Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="4" t="n">
         <v>46216.72708333333</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="5">
         <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),F36-E36,"")</f>
         <v/>
       </c>
@@ -2200,10 +2201,10 @@
           <t>Service interruption of 5 (2G)(4G) xD sites at certain parts of Kinabatangan, Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E37" s="4" t="n">
         <v>46216.72708333333</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37" s="5">
         <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),F37-E37,"")</f>
         <v/>
       </c>
@@ -2239,10 +2240,10 @@
           <t>Service interruption of 5 (2G)(4G) xD sites at certain parts of Kinabatangan, Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" s="4" t="n">
         <v>46216.72708333333</v>
       </c>
-      <c r="G38" s="3">
+      <c r="G38" s="5">
         <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),F38-E38,"")</f>
         <v/>
       </c>
@@ -2278,10 +2279,10 @@
           <t>Service interruption of 5 (2G)(4G) xD sites at certain parts of Kinabatangan, Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" s="4" t="n">
         <v>46216.72708333333</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39" s="5">
         <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),F39-E39,"")</f>
         <v/>
       </c>
@@ -2317,10 +2318,10 @@
           <t>Service interruption of 7 (2G)(4G) xD sites at certain parts of Rawang 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="E40" s="4" t="n">
         <v>46216.69444444445</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40" s="5">
         <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),F40-E40,"")</f>
         <v/>
       </c>
@@ -2356,10 +2357,10 @@
           <t>Service interruption of 7 (2G)(4G) xD sites at certain parts of Rawang 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="E41" s="4" t="n">
         <v>46216.69444444445</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="5">
         <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),F41-E41,"")</f>
         <v/>
       </c>
@@ -2395,10 +2396,10 @@
           <t>Service interruption of 7 (2G)(4G) xD sites at certain parts of Rawang 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="4" t="n">
         <v>46216.69444444445</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="5">
         <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),F42-E42,"")</f>
         <v/>
       </c>
@@ -2434,10 +2435,10 @@
           <t>Service interruption of 7 (2G)(4G) xD sites at certain parts of Rawang 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E43" s="4" t="n">
         <v>46216.69444444445</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="5">
         <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),F43-E43,"")</f>
         <v/>
       </c>
@@ -2473,10 +2474,10 @@
           <t>Service interruption of 7 (2G)(4G) xD sites at certain parts of Rawang 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="E44" s="4" t="n">
         <v>46216.69444444445</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="5">
         <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),F44-E44,"")</f>
         <v/>
       </c>
@@ -2512,10 +2513,10 @@
           <t>Service interruption of 7 (2G)(4G) xD sites at certain parts of Rawang 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="E45" s="4" t="n">
         <v>46216.69444444445</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="5">
         <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),F45-E45,"")</f>
         <v/>
       </c>
@@ -2551,10 +2552,10 @@
           <t>Service interruption of 7 (2G)(4G) xD sites at certain parts of Rawang 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" s="4" t="n">
         <v>46216.69444444445</v>
       </c>
-      <c r="G46" s="3">
+      <c r="G46" s="5">
         <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),F46-E46,"")</f>
         <v/>
       </c>
@@ -2590,13 +2591,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E47" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="F47" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="5">
         <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),F47-E47,"")</f>
         <v/>
       </c>
@@ -2642,13 +2643,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E48" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="F48" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="5">
         <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),F48-E48,"")</f>
         <v/>
       </c>
@@ -2694,13 +2695,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E49" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="F49" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49" s="5">
         <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),F49-E49,"")</f>
         <v/>
       </c>
@@ -2746,13 +2747,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="E50" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="F50" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G50" s="5">
         <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),F50-E50,"")</f>
         <v/>
       </c>
@@ -2798,13 +2799,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="E51" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="F51" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51" s="5">
         <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),F51-E51,"")</f>
         <v/>
       </c>
@@ -2850,13 +2851,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="E52" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="F52" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="5">
         <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),F52-E52,"")</f>
         <v/>
       </c>
@@ -2902,13 +2903,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="E53" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="F53" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G53" s="5">
         <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),F53-E53,"")</f>
         <v/>
       </c>
@@ -2954,13 +2955,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="E54" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F54" s="2" t="n">
+      <c r="F54" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54" s="5">
         <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),F54-E54,"")</f>
         <v/>
       </c>
@@ -3006,13 +3007,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="E55" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="F55" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G55" s="3">
+      <c r="G55" s="5">
         <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),F55-E55,"")</f>
         <v/>
       </c>
@@ -3058,13 +3059,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E56" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="F56" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G56" s="5">
         <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),F56-E56,"")</f>
         <v/>
       </c>
@@ -3110,13 +3111,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E57" s="2" t="n">
+      <c r="E57" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="F57" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="5">
         <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),F57-E57,"")</f>
         <v/>
       </c>
@@ -3162,13 +3163,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E58" s="2" t="n">
+      <c r="E58" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F58" s="2" t="n">
+      <c r="F58" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="5">
         <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),F58-E58,"")</f>
         <v/>
       </c>
@@ -3214,13 +3215,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="E59" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="F59" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="5">
         <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),F59-E59,"")</f>
         <v/>
       </c>
@@ -3266,13 +3267,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E60" s="2" t="n">
+      <c r="E60" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F60" s="2" t="n">
+      <c r="F60" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G60" s="3">
+      <c r="G60" s="5">
         <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),F60-E60,"")</f>
         <v/>
       </c>
@@ -3318,13 +3319,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E61" s="2" t="n">
+      <c r="E61" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="F61" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G61" s="5">
         <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),F61-E61,"")</f>
         <v/>
       </c>
@@ -3370,13 +3371,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E62" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="F62" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="5">
         <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),F62-E62,"")</f>
         <v/>
       </c>
@@ -3422,13 +3423,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E63" s="2" t="n">
+      <c r="E63" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="F63" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G63" s="3">
+      <c r="G63" s="5">
         <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),F63-E63,"")</f>
         <v/>
       </c>
@@ -3474,13 +3475,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E64" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="F64" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G64" s="3">
+      <c r="G64" s="5">
         <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),F64-E64,"")</f>
         <v/>
       </c>
@@ -3526,13 +3527,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="E65" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="F65" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G65" s="3">
+      <c r="G65" s="5">
         <f>IF(AND(E65&lt;&gt;"",F65&lt;&gt;""),F65-E65,"")</f>
         <v/>
       </c>
@@ -3578,13 +3579,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="E66" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="F66" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G66" s="3">
+      <c r="G66" s="5">
         <f>IF(AND(E66&lt;&gt;"",F66&lt;&gt;""),F66-E66,"")</f>
         <v/>
       </c>
@@ -3630,13 +3631,13 @@
           <t>Service interruption of 20 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Bentong area, Pahang</t>
         </is>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E67" s="4" t="n">
         <v>46216.68125</v>
       </c>
-      <c r="F67" s="2" t="n">
+      <c r="F67" s="4" t="n">
         <v>46217.03680555556</v>
       </c>
-      <c r="G67" s="3">
+      <c r="G67" s="5">
         <f>IF(AND(E67&lt;&gt;"",F67&lt;&gt;""),F67-E67,"")</f>
         <v/>
       </c>
@@ -3682,10 +3683,10 @@
           <t>Service interruption of 5 (2G)(4G) xD sites at certain parts of Batu Caves 2 / Genting area, Selangor, Pahang</t>
         </is>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="E68" s="4" t="n">
         <v>46216.67986111111</v>
       </c>
-      <c r="G68" s="3">
+      <c r="G68" s="5">
         <f>IF(AND(E68&lt;&gt;"",F68&lt;&gt;""),F68-E68,"")</f>
         <v/>
       </c>
@@ -3721,10 +3722,10 @@
           <t>Service interruption of 5 (2G)(4G) xD sites at certain parts of Batu Caves 2 / Genting area, Selangor, Pahang</t>
         </is>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="E69" s="4" t="n">
         <v>46216.67986111111</v>
       </c>
-      <c r="G69" s="3">
+      <c r="G69" s="5">
         <f>IF(AND(E69&lt;&gt;"",F69&lt;&gt;""),F69-E69,"")</f>
         <v/>
       </c>
@@ -3760,10 +3761,10 @@
           <t>Service interruption of 5 (2G)(4G) xD sites at certain parts of Batu Caves 2 / Genting area, Selangor, Pahang</t>
         </is>
       </c>
-      <c r="E70" s="2" t="n">
+      <c r="E70" s="4" t="n">
         <v>46216.67986111111</v>
       </c>
-      <c r="G70" s="3">
+      <c r="G70" s="5">
         <f>IF(AND(E70&lt;&gt;"",F70&lt;&gt;""),F70-E70,"")</f>
         <v/>
       </c>
@@ -3799,10 +3800,10 @@
           <t>Service interruption of 5 (2G)(4G) xD sites at certain parts of Batu Caves 2 / Genting area, Selangor, Pahang</t>
         </is>
       </c>
-      <c r="E71" s="2" t="n">
+      <c r="E71" s="4" t="n">
         <v>46216.67986111111</v>
       </c>
-      <c r="G71" s="3">
+      <c r="G71" s="5">
         <f>IF(AND(E71&lt;&gt;"",F71&lt;&gt;""),F71-E71,"")</f>
         <v/>
       </c>
@@ -3838,10 +3839,10 @@
           <t>Service interruption of 5 (2G)(4G) xD sites at certain parts of Batu Caves 2 / Genting area, Selangor, Pahang</t>
         </is>
       </c>
-      <c r="E72" s="2" t="n">
+      <c r="E72" s="4" t="n">
         <v>46216.67986111111</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="5">
         <f>IF(AND(E72&lt;&gt;"",F72&lt;&gt;""),F72-E72,"")</f>
         <v/>
       </c>
@@ -3877,10 +3878,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="E73" s="4" t="n">
         <v>46216.67430555556</v>
       </c>
-      <c r="G73" s="3">
+      <c r="G73" s="5">
         <f>IF(AND(E73&lt;&gt;"",F73&lt;&gt;""),F73-E73,"")</f>
         <v/>
       </c>
@@ -3916,10 +3917,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E74" s="2" t="n">
+      <c r="E74" s="4" t="n">
         <v>46216.67430555556</v>
       </c>
-      <c r="G74" s="3">
+      <c r="G74" s="5">
         <f>IF(AND(E74&lt;&gt;"",F74&lt;&gt;""),F74-E74,"")</f>
         <v/>
       </c>
@@ -3955,10 +3956,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E75" s="2" t="n">
+      <c r="E75" s="4" t="n">
         <v>46216.67430555556</v>
       </c>
-      <c r="G75" s="3">
+      <c r="G75" s="5">
         <f>IF(AND(E75&lt;&gt;"",F75&lt;&gt;""),F75-E75,"")</f>
         <v/>
       </c>
@@ -3994,10 +3995,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E76" s="2" t="n">
+      <c r="E76" s="4" t="n">
         <v>46216.67430555556</v>
       </c>
-      <c r="G76" s="3">
+      <c r="G76" s="5">
         <f>IF(AND(E76&lt;&gt;"",F76&lt;&gt;""),F76-E76,"")</f>
         <v/>
       </c>
@@ -4033,10 +4034,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E77" s="2" t="n">
+      <c r="E77" s="4" t="n">
         <v>46216.67430555556</v>
       </c>
-      <c r="G77" s="3">
+      <c r="G77" s="5">
         <f>IF(AND(E77&lt;&gt;"",F77&lt;&gt;""),F77-E77,"")</f>
         <v/>
       </c>
@@ -4072,10 +4073,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="E78" s="4" t="n">
         <v>46216.67430555556</v>
       </c>
-      <c r="G78" s="3">
+      <c r="G78" s="5">
         <f>IF(AND(E78&lt;&gt;"",F78&lt;&gt;""),F78-E78,"")</f>
         <v/>
       </c>
@@ -4111,10 +4112,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E79" s="2" t="n">
+      <c r="E79" s="4" t="n">
         <v>46216.67430555556</v>
       </c>
-      <c r="G79" s="3">
+      <c r="G79" s="5">
         <f>IF(AND(E79&lt;&gt;"",F79&lt;&gt;""),F79-E79,"")</f>
         <v/>
       </c>
@@ -4150,13 +4151,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E80" s="2" t="n">
+      <c r="E80" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F80" s="2" t="n">
+      <c r="F80" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G80" s="3">
+      <c r="G80" s="5">
         <f>IF(AND(E80&lt;&gt;"",F80&lt;&gt;""),F80-E80,"")</f>
         <v/>
       </c>
@@ -4202,13 +4203,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E81" s="2" t="n">
+      <c r="E81" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F81" s="2" t="n">
+      <c r="F81" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G81" s="3">
+      <c r="G81" s="5">
         <f>IF(AND(E81&lt;&gt;"",F81&lt;&gt;""),F81-E81,"")</f>
         <v/>
       </c>
@@ -4254,13 +4255,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E82" s="2" t="n">
+      <c r="E82" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F82" s="2" t="n">
+      <c r="F82" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G82" s="3">
+      <c r="G82" s="5">
         <f>IF(AND(E82&lt;&gt;"",F82&lt;&gt;""),F82-E82,"")</f>
         <v/>
       </c>
@@ -4306,13 +4307,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E83" s="2" t="n">
+      <c r="E83" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F83" s="2" t="n">
+      <c r="F83" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="5">
         <f>IF(AND(E83&lt;&gt;"",F83&lt;&gt;""),F83-E83,"")</f>
         <v/>
       </c>
@@ -4358,13 +4359,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E84" s="2" t="n">
+      <c r="E84" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F84" s="2" t="n">
+      <c r="F84" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G84" s="3">
+      <c r="G84" s="5">
         <f>IF(AND(E84&lt;&gt;"",F84&lt;&gt;""),F84-E84,"")</f>
         <v/>
       </c>
@@ -4410,13 +4411,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E85" s="2" t="n">
+      <c r="E85" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F85" s="2" t="n">
+      <c r="F85" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G85" s="3">
+      <c r="G85" s="5">
         <f>IF(AND(E85&lt;&gt;"",F85&lt;&gt;""),F85-E85,"")</f>
         <v/>
       </c>
@@ -4462,13 +4463,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E86" s="2" t="n">
+      <c r="E86" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F86" s="2" t="n">
+      <c r="F86" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G86" s="3">
+      <c r="G86" s="5">
         <f>IF(AND(E86&lt;&gt;"",F86&lt;&gt;""),F86-E86,"")</f>
         <v/>
       </c>
@@ -4514,13 +4515,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E87" s="2" t="n">
+      <c r="E87" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F87" s="2" t="n">
+      <c r="F87" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G87" s="3">
+      <c r="G87" s="5">
         <f>IF(AND(E87&lt;&gt;"",F87&lt;&gt;""),F87-E87,"")</f>
         <v/>
       </c>
@@ -4566,13 +4567,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E88" s="2" t="n">
+      <c r="E88" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F88" s="2" t="n">
+      <c r="F88" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G88" s="3">
+      <c r="G88" s="5">
         <f>IF(AND(E88&lt;&gt;"",F88&lt;&gt;""),F88-E88,"")</f>
         <v/>
       </c>
@@ -4618,13 +4619,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E89" s="2" t="n">
+      <c r="E89" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F89" s="2" t="n">
+      <c r="F89" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G89" s="5">
         <f>IF(AND(E89&lt;&gt;"",F89&lt;&gt;""),F89-E89,"")</f>
         <v/>
       </c>
@@ -4670,13 +4671,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E90" s="2" t="n">
+      <c r="E90" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F90" s="2" t="n">
+      <c r="F90" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G90" s="3">
+      <c r="G90" s="5">
         <f>IF(AND(E90&lt;&gt;"",F90&lt;&gt;""),F90-E90,"")</f>
         <v/>
       </c>
@@ -4722,13 +4723,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E91" s="2" t="n">
+      <c r="E91" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F91" s="2" t="n">
+      <c r="F91" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="5">
         <f>IF(AND(E91&lt;&gt;"",F91&lt;&gt;""),F91-E91,"")</f>
         <v/>
       </c>
@@ -4774,13 +4775,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E92" s="2" t="n">
+      <c r="E92" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F92" s="2" t="n">
+      <c r="F92" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G92" s="3">
+      <c r="G92" s="5">
         <f>IF(AND(E92&lt;&gt;"",F92&lt;&gt;""),F92-E92,"")</f>
         <v/>
       </c>
@@ -4826,13 +4827,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E93" s="2" t="n">
+      <c r="E93" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F93" s="2" t="n">
+      <c r="F93" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G93" s="3">
+      <c r="G93" s="5">
         <f>IF(AND(E93&lt;&gt;"",F93&lt;&gt;""),F93-E93,"")</f>
         <v/>
       </c>
@@ -4878,13 +4879,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E94" s="2" t="n">
+      <c r="E94" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F94" s="2" t="n">
+      <c r="F94" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G94" s="5">
         <f>IF(AND(E94&lt;&gt;"",F94&lt;&gt;""),F94-E94,"")</f>
         <v/>
       </c>
@@ -4930,13 +4931,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E95" s="2" t="n">
+      <c r="E95" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F95" s="2" t="n">
+      <c r="F95" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G95" s="3">
+      <c r="G95" s="5">
         <f>IF(AND(E95&lt;&gt;"",F95&lt;&gt;""),F95-E95,"")</f>
         <v/>
       </c>
@@ -4982,13 +4983,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Bintulu 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E96" s="2" t="n">
+      <c r="E96" s="4" t="n">
         <v>46216.64305555556</v>
       </c>
-      <c r="F96" s="2" t="n">
+      <c r="F96" s="4" t="n">
         <v>46216.71180555555</v>
       </c>
-      <c r="G96" s="3">
+      <c r="G96" s="5">
         <f>IF(AND(E96&lt;&gt;"",F96&lt;&gt;""),F96-E96,"")</f>
         <v/>
       </c>
@@ -5034,13 +5035,13 @@
           <t>Service interruption of 3 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E97" s="2" t="n">
+      <c r="E97" s="4" t="n">
         <v>46216.63888888889</v>
       </c>
-      <c r="F97" s="2" t="n">
+      <c r="F97" s="4" t="n">
         <v>46216.90416666667</v>
       </c>
-      <c r="G97" s="3">
+      <c r="G97" s="5">
         <f>IF(AND(E97&lt;&gt;"",F97&lt;&gt;""),F97-E97,"")</f>
         <v/>
       </c>
@@ -5086,13 +5087,13 @@
           <t>Service interruption of 3 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E98" s="2" t="n">
+      <c r="E98" s="4" t="n">
         <v>46216.63888888889</v>
       </c>
-      <c r="F98" s="2" t="n">
+      <c r="F98" s="4" t="n">
         <v>46216.90416666667</v>
       </c>
-      <c r="G98" s="3">
+      <c r="G98" s="5">
         <f>IF(AND(E98&lt;&gt;"",F98&lt;&gt;""),F98-E98,"")</f>
         <v/>
       </c>
@@ -5138,13 +5139,13 @@
           <t>Service interruption of 3 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E99" s="2" t="n">
+      <c r="E99" s="4" t="n">
         <v>46216.63888888889</v>
       </c>
-      <c r="F99" s="2" t="n">
+      <c r="F99" s="4" t="n">
         <v>46216.90416666667</v>
       </c>
-      <c r="G99" s="3">
+      <c r="G99" s="5">
         <f>IF(AND(E99&lt;&gt;"",F99&lt;&gt;""),F99-E99,"")</f>
         <v/>
       </c>
@@ -5190,13 +5191,13 @@
           <t>Service interruption of 3 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E100" s="2" t="n">
+      <c r="E100" s="4" t="n">
         <v>46216.63888888889</v>
       </c>
-      <c r="F100" s="2" t="n">
+      <c r="F100" s="4" t="n">
         <v>46216.90416666667</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G100" s="5">
         <f>IF(AND(E100&lt;&gt;"",F100&lt;&gt;""),F100-E100,"")</f>
         <v/>
       </c>
@@ -5242,13 +5243,13 @@
           <t>Service interruption of 3 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E101" s="2" t="n">
+      <c r="E101" s="4" t="n">
         <v>46216.63888888889</v>
       </c>
-      <c r="F101" s="2" t="n">
+      <c r="F101" s="4" t="n">
         <v>46216.90416666667</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101" s="5">
         <f>IF(AND(E101&lt;&gt;"",F101&lt;&gt;""),F101-E101,"")</f>
         <v/>
       </c>
@@ -5294,13 +5295,13 @@
           <t>Service interruption of 3 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E102" s="2" t="n">
+      <c r="E102" s="4" t="n">
         <v>46216.63888888889</v>
       </c>
-      <c r="F102" s="2" t="n">
+      <c r="F102" s="4" t="n">
         <v>46216.90416666667</v>
       </c>
-      <c r="G102" s="3">
+      <c r="G102" s="5">
         <f>IF(AND(E102&lt;&gt;"",F102&lt;&gt;""),F102-E102,"")</f>
         <v/>
       </c>
@@ -5346,13 +5347,13 @@
           <t>Service interruption of 3 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E103" s="2" t="n">
+      <c r="E103" s="4" t="n">
         <v>46216.63888888889</v>
       </c>
-      <c r="F103" s="2" t="n">
+      <c r="F103" s="4" t="n">
         <v>46216.90416666667</v>
       </c>
-      <c r="G103" s="3">
+      <c r="G103" s="5">
         <f>IF(AND(E103&lt;&gt;"",F103&lt;&gt;""),F103-E103,"")</f>
         <v/>
       </c>
@@ -5398,13 +5399,13 @@
           <t>Service interruption of 3 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E104" s="2" t="n">
+      <c r="E104" s="4" t="n">
         <v>46216.63888888889</v>
       </c>
-      <c r="F104" s="2" t="n">
+      <c r="F104" s="4" t="n">
         <v>46216.90416666667</v>
       </c>
-      <c r="G104" s="3">
+      <c r="G104" s="5">
         <f>IF(AND(E104&lt;&gt;"",F104&lt;&gt;""),F104-E104,"")</f>
         <v/>
       </c>
@@ -5450,13 +5451,13 @@
           <t>Service interruption of 3 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E105" s="2" t="n">
+      <c r="E105" s="4" t="n">
         <v>46216.63888888889</v>
       </c>
-      <c r="F105" s="2" t="n">
+      <c r="F105" s="4" t="n">
         <v>46216.90416666667</v>
       </c>
-      <c r="G105" s="3">
+      <c r="G105" s="5">
         <f>IF(AND(E105&lt;&gt;"",F105&lt;&gt;""),F105-E105,"")</f>
         <v/>
       </c>
@@ -5502,13 +5503,13 @@
           <t>Service interruption of 3 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E106" s="2" t="n">
+      <c r="E106" s="4" t="n">
         <v>46216.63888888889</v>
       </c>
-      <c r="F106" s="2" t="n">
+      <c r="F106" s="4" t="n">
         <v>46216.90416666667</v>
       </c>
-      <c r="G106" s="3">
+      <c r="G106" s="5">
         <f>IF(AND(E106&lt;&gt;"",F106&lt;&gt;""),F106-E106,"")</f>
         <v/>
       </c>
@@ -5554,13 +5555,13 @@
           <t>Service interruption of 3 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E107" s="2" t="n">
+      <c r="E107" s="4" t="n">
         <v>46216.63888888889</v>
       </c>
-      <c r="F107" s="2" t="n">
+      <c r="F107" s="4" t="n">
         <v>46216.90416666667</v>
       </c>
-      <c r="G107" s="3">
+      <c r="G107" s="5">
         <f>IF(AND(E107&lt;&gt;"",F107&lt;&gt;""),F107-E107,"")</f>
         <v/>
       </c>
@@ -5606,10 +5607,10 @@
           <t>Service interruption of 7 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Kota Belud area, Sabah</t>
         </is>
       </c>
-      <c r="E108" s="2" t="n">
+      <c r="E108" s="4" t="n">
         <v>46216.60069444445</v>
       </c>
-      <c r="G108" s="3">
+      <c r="G108" s="5">
         <f>IF(AND(E108&lt;&gt;"",F108&lt;&gt;""),F108-E108,"")</f>
         <v/>
       </c>
@@ -5645,10 +5646,10 @@
           <t>Service interruption of 7 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Kota Belud area, Sabah</t>
         </is>
       </c>
-      <c r="E109" s="2" t="n">
+      <c r="E109" s="4" t="n">
         <v>46216.60069444445</v>
       </c>
-      <c r="G109" s="3">
+      <c r="G109" s="5">
         <f>IF(AND(E109&lt;&gt;"",F109&lt;&gt;""),F109-E109,"")</f>
         <v/>
       </c>
@@ -5684,10 +5685,10 @@
           <t>Service interruption of 7 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Kota Belud area, Sabah</t>
         </is>
       </c>
-      <c r="E110" s="2" t="n">
+      <c r="E110" s="4" t="n">
         <v>46216.60069444445</v>
       </c>
-      <c r="G110" s="3">
+      <c r="G110" s="5">
         <f>IF(AND(E110&lt;&gt;"",F110&lt;&gt;""),F110-E110,"")</f>
         <v/>
       </c>
@@ -5723,10 +5724,10 @@
           <t>Service interruption of 7 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Kota Belud area, Sabah</t>
         </is>
       </c>
-      <c r="E111" s="2" t="n">
+      <c r="E111" s="4" t="n">
         <v>46216.60069444445</v>
       </c>
-      <c r="G111" s="3">
+      <c r="G111" s="5">
         <f>IF(AND(E111&lt;&gt;"",F111&lt;&gt;""),F111-E111,"")</f>
         <v/>
       </c>
@@ -5762,10 +5763,10 @@
           <t>Service interruption of 7 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Kota Belud area, Sabah</t>
         </is>
       </c>
-      <c r="E112" s="2" t="n">
+      <c r="E112" s="4" t="n">
         <v>46216.60069444445</v>
       </c>
-      <c r="G112" s="3">
+      <c r="G112" s="5">
         <f>IF(AND(E112&lt;&gt;"",F112&lt;&gt;""),F112-E112,"")</f>
         <v/>
       </c>
@@ -5801,10 +5802,10 @@
           <t>Service interruption of 7 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Kota Belud area, Sabah</t>
         </is>
       </c>
-      <c r="E113" s="2" t="n">
+      <c r="E113" s="4" t="n">
         <v>46216.60069444445</v>
       </c>
-      <c r="G113" s="3">
+      <c r="G113" s="5">
         <f>IF(AND(E113&lt;&gt;"",F113&lt;&gt;""),F113-E113,"")</f>
         <v/>
       </c>
@@ -5840,10 +5841,10 @@
           <t>Service interruption of 7 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Kota Belud area, Sabah</t>
         </is>
       </c>
-      <c r="E114" s="2" t="n">
+      <c r="E114" s="4" t="n">
         <v>46216.60069444445</v>
       </c>
-      <c r="G114" s="3">
+      <c r="G114" s="5">
         <f>IF(AND(E114&lt;&gt;"",F114&lt;&gt;""),F114-E114,"")</f>
         <v/>
       </c>
@@ -5879,10 +5880,10 @@
           <t>Service interruption of 7 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Kota Belud area, Sabah</t>
         </is>
       </c>
-      <c r="E115" s="2" t="n">
+      <c r="E115" s="4" t="n">
         <v>46216.60069444445</v>
       </c>
-      <c r="G115" s="3">
+      <c r="G115" s="5">
         <f>IF(AND(E115&lt;&gt;"",F115&lt;&gt;""),F115-E115,"")</f>
         <v/>
       </c>
@@ -5918,10 +5919,10 @@
           <t>Service interruption of 7 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Kota Belud area, Sabah</t>
         </is>
       </c>
-      <c r="E116" s="2" t="n">
+      <c r="E116" s="4" t="n">
         <v>46216.60069444445</v>
       </c>
-      <c r="G116" s="3">
+      <c r="G116" s="5">
         <f>IF(AND(E116&lt;&gt;"",F116&lt;&gt;""),F116-E116,"")</f>
         <v/>
       </c>
@@ -5957,10 +5958,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kuala Kangsar, Hulu Perak area, Perak</t>
         </is>
       </c>
-      <c r="E117" s="2" t="n">
+      <c r="E117" s="4" t="n">
         <v>46216.58680555555</v>
       </c>
-      <c r="G117" s="3">
+      <c r="G117" s="5">
         <f>IF(AND(E117&lt;&gt;"",F117&lt;&gt;""),F117-E117,"")</f>
         <v/>
       </c>
@@ -5996,10 +5997,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kuala Kangsar, Hulu Perak area, Perak</t>
         </is>
       </c>
-      <c r="E118" s="2" t="n">
+      <c r="E118" s="4" t="n">
         <v>46216.58680555555</v>
       </c>
-      <c r="G118" s="3">
+      <c r="G118" s="5">
         <f>IF(AND(E118&lt;&gt;"",F118&lt;&gt;""),F118-E118,"")</f>
         <v/>
       </c>
@@ -6035,10 +6036,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kuala Kangsar, Hulu Perak area, Perak</t>
         </is>
       </c>
-      <c r="E119" s="2" t="n">
+      <c r="E119" s="4" t="n">
         <v>46216.58680555555</v>
       </c>
-      <c r="G119" s="3">
+      <c r="G119" s="5">
         <f>IF(AND(E119&lt;&gt;"",F119&lt;&gt;""),F119-E119,"")</f>
         <v/>
       </c>
@@ -6074,10 +6075,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kuala Kangsar, Hulu Perak area, Perak</t>
         </is>
       </c>
-      <c r="E120" s="2" t="n">
+      <c r="E120" s="4" t="n">
         <v>46216.58680555555</v>
       </c>
-      <c r="G120" s="3">
+      <c r="G120" s="5">
         <f>IF(AND(E120&lt;&gt;"",F120&lt;&gt;""),F120-E120,"")</f>
         <v/>
       </c>
@@ -6113,10 +6114,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kuala Kangsar, Hulu Perak area, Perak</t>
         </is>
       </c>
-      <c r="E121" s="2" t="n">
+      <c r="E121" s="4" t="n">
         <v>46216.58680555555</v>
       </c>
-      <c r="G121" s="3">
+      <c r="G121" s="5">
         <f>IF(AND(E121&lt;&gt;"",F121&lt;&gt;""),F121-E121,"")</f>
         <v/>
       </c>
@@ -6152,10 +6153,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kuala Kangsar, Hulu Perak area, Perak</t>
         </is>
       </c>
-      <c r="E122" s="2" t="n">
+      <c r="E122" s="4" t="n">
         <v>46216.58680555555</v>
       </c>
-      <c r="G122" s="3">
+      <c r="G122" s="5">
         <f>IF(AND(E122&lt;&gt;"",F122&lt;&gt;""),F122-E122,"")</f>
         <v/>
       </c>
@@ -6191,10 +6192,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kuala Kangsar, Hulu Perak area, Perak</t>
         </is>
       </c>
-      <c r="E123" s="2" t="n">
+      <c r="E123" s="4" t="n">
         <v>46216.58680555555</v>
       </c>
-      <c r="G123" s="3">
+      <c r="G123" s="5">
         <f>IF(AND(E123&lt;&gt;"",F123&lt;&gt;""),F123-E123,"")</f>
         <v/>
       </c>
@@ -6230,10 +6231,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kuala Kangsar, Hulu Perak area, Perak</t>
         </is>
       </c>
-      <c r="E124" s="2" t="n">
+      <c r="E124" s="4" t="n">
         <v>46216.58680555555</v>
       </c>
-      <c r="G124" s="3">
+      <c r="G124" s="5">
         <f>IF(AND(E124&lt;&gt;"",F124&lt;&gt;""),F124-E124,"")</f>
         <v/>
       </c>
@@ -6269,13 +6270,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Banting / Jenjarum, Banting / Jenjarum 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E125" s="4" t="n">
         <v>46216.55</v>
       </c>
-      <c r="F125" s="2" t="n">
+      <c r="F125" s="4" t="n">
         <v>46216.77291666667</v>
       </c>
-      <c r="G125" s="3">
+      <c r="G125" s="5">
         <f>IF(AND(E125&lt;&gt;"",F125&lt;&gt;""),F125-E125,"")</f>
         <v/>
       </c>
@@ -6321,13 +6322,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Banting / Jenjarum, Banting / Jenjarum 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E126" s="2" t="n">
+      <c r="E126" s="4" t="n">
         <v>46216.55</v>
       </c>
-      <c r="F126" s="2" t="n">
+      <c r="F126" s="4" t="n">
         <v>46216.77291666667</v>
       </c>
-      <c r="G126" s="3">
+      <c r="G126" s="5">
         <f>IF(AND(E126&lt;&gt;"",F126&lt;&gt;""),F126-E126,"")</f>
         <v/>
       </c>
@@ -6373,13 +6374,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Banting / Jenjarum, Banting / Jenjarum 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E127" s="4" t="n">
         <v>46216.55</v>
       </c>
-      <c r="F127" s="2" t="n">
+      <c r="F127" s="4" t="n">
         <v>46216.77291666667</v>
       </c>
-      <c r="G127" s="3">
+      <c r="G127" s="5">
         <f>IF(AND(E127&lt;&gt;"",F127&lt;&gt;""),F127-E127,"")</f>
         <v/>
       </c>
@@ -6425,13 +6426,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Banting / Jenjarum, Banting / Jenjarum 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E128" s="2" t="n">
+      <c r="E128" s="4" t="n">
         <v>46216.55</v>
       </c>
-      <c r="F128" s="2" t="n">
+      <c r="F128" s="4" t="n">
         <v>46216.77291666667</v>
       </c>
-      <c r="G128" s="3">
+      <c r="G128" s="5">
         <f>IF(AND(E128&lt;&gt;"",F128&lt;&gt;""),F128-E128,"")</f>
         <v/>
       </c>
@@ -6477,13 +6478,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Banting / Jenjarum, Banting / Jenjarum 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E129" s="2" t="n">
+      <c r="E129" s="4" t="n">
         <v>46216.55</v>
       </c>
-      <c r="F129" s="2" t="n">
+      <c r="F129" s="4" t="n">
         <v>46216.77291666667</v>
       </c>
-      <c r="G129" s="3">
+      <c r="G129" s="5">
         <f>IF(AND(E129&lt;&gt;"",F129&lt;&gt;""),F129-E129,"")</f>
         <v/>
       </c>
@@ -6529,13 +6530,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Banting / Jenjarum, Banting / Jenjarum 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E130" s="2" t="n">
+      <c r="E130" s="4" t="n">
         <v>46216.55</v>
       </c>
-      <c r="F130" s="2" t="n">
+      <c r="F130" s="4" t="n">
         <v>46216.77291666667</v>
       </c>
-      <c r="G130" s="3">
+      <c r="G130" s="5">
         <f>IF(AND(E130&lt;&gt;"",F130&lt;&gt;""),F130-E130,"")</f>
         <v/>
       </c>
@@ -6581,13 +6582,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Banting / Jenjarum, Banting / Jenjarum 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E131" s="2" t="n">
+      <c r="E131" s="4" t="n">
         <v>46216.55</v>
       </c>
-      <c r="F131" s="2" t="n">
+      <c r="F131" s="4" t="n">
         <v>46216.77291666667</v>
       </c>
-      <c r="G131" s="3">
+      <c r="G131" s="5">
         <f>IF(AND(E131&lt;&gt;"",F131&lt;&gt;""),F131-E131,"")</f>
         <v/>
       </c>
@@ -6633,13 +6634,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Banting / Jenjarum, Banting / Jenjarum 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E132" s="2" t="n">
+      <c r="E132" s="4" t="n">
         <v>46216.55</v>
       </c>
-      <c r="F132" s="2" t="n">
+      <c r="F132" s="4" t="n">
         <v>46216.77291666667</v>
       </c>
-      <c r="G132" s="3">
+      <c r="G132" s="5">
         <f>IF(AND(E132&lt;&gt;"",F132&lt;&gt;""),F132-E132,"")</f>
         <v/>
       </c>
@@ -6685,13 +6686,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Banting / Jenjarum, Banting / Jenjarum 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E133" s="2" t="n">
+      <c r="E133" s="4" t="n">
         <v>46216.55</v>
       </c>
-      <c r="F133" s="2" t="n">
+      <c r="F133" s="4" t="n">
         <v>46216.77291666667</v>
       </c>
-      <c r="G133" s="3">
+      <c r="G133" s="5">
         <f>IF(AND(E133&lt;&gt;"",F133&lt;&gt;""),F133-E133,"")</f>
         <v/>
       </c>
@@ -6737,13 +6738,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Banting / Jenjarum, Banting / Jenjarum 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E134" s="2" t="n">
+      <c r="E134" s="4" t="n">
         <v>46216.55</v>
       </c>
-      <c r="F134" s="2" t="n">
+      <c r="F134" s="4" t="n">
         <v>46216.77291666667</v>
       </c>
-      <c r="G134" s="3">
+      <c r="G134" s="5">
         <f>IF(AND(E134&lt;&gt;"",F134&lt;&gt;""),F134-E134,"")</f>
         <v/>
       </c>
@@ -6789,13 +6790,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Banting / Jenjarum, Banting / Jenjarum 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E135" s="2" t="n">
+      <c r="E135" s="4" t="n">
         <v>46216.55</v>
       </c>
-      <c r="F135" s="2" t="n">
+      <c r="F135" s="4" t="n">
         <v>46216.77291666667</v>
       </c>
-      <c r="G135" s="3">
+      <c r="G135" s="5">
         <f>IF(AND(E135&lt;&gt;"",F135&lt;&gt;""),F135-E135,"")</f>
         <v/>
       </c>
@@ -6841,10 +6842,10 @@
           <t>Service interruption of 9 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Banting / Jenjarum, Banting / Jenjarum 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E136" s="2" t="n">
+      <c r="E136" s="4" t="n">
         <v>46216.55</v>
       </c>
-      <c r="G136" s="3">
+      <c r="G136" s="5">
         <f>IF(AND(E136&lt;&gt;"",F136&lt;&gt;""),F136-E136,"")</f>
         <v/>
       </c>
@@ -6880,10 +6881,10 @@
           <t>Service interruption of 9 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Banting / Jenjarum, Banting / Jenjarum 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E137" s="2" t="n">
+      <c r="E137" s="4" t="n">
         <v>46216.55</v>
       </c>
-      <c r="G137" s="3">
+      <c r="G137" s="5">
         <f>IF(AND(E137&lt;&gt;"",F137&lt;&gt;""),F137-E137,"")</f>
         <v/>
       </c>
@@ -6919,10 +6920,10 @@
           <t>Service interruption of 9 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Banting / Jenjarum, Banting / Jenjarum 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E138" s="2" t="n">
+      <c r="E138" s="4" t="n">
         <v>46216.55</v>
       </c>
-      <c r="G138" s="3">
+      <c r="G138" s="5">
         <f>IF(AND(E138&lt;&gt;"",F138&lt;&gt;""),F138-E138,"")</f>
         <v/>
       </c>
@@ -6958,10 +6959,10 @@
           <t>Service interruption of 9 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Banting / Jenjarum, Banting / Jenjarum 1 area, Selangor</t>
         </is>
       </c>
-      <c r="E139" s="2" t="n">
+      <c r="E139" s="4" t="n">
         <v>46216.55</v>
       </c>
-      <c r="G139" s="3">
+      <c r="G139" s="5">
         <f>IF(AND(E139&lt;&gt;"",F139&lt;&gt;""),F139-E139,"")</f>
         <v/>
       </c>
@@ -6997,13 +6998,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E140" s="2" t="n">
+      <c r="E140" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F140" s="2" t="n">
+      <c r="F140" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G140" s="3">
+      <c r="G140" s="5">
         <f>IF(AND(E140&lt;&gt;"",F140&lt;&gt;""),F140-E140,"")</f>
         <v/>
       </c>
@@ -7049,13 +7050,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E141" s="2" t="n">
+      <c r="E141" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F141" s="2" t="n">
+      <c r="F141" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G141" s="3">
+      <c r="G141" s="5">
         <f>IF(AND(E141&lt;&gt;"",F141&lt;&gt;""),F141-E141,"")</f>
         <v/>
       </c>
@@ -7101,13 +7102,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E142" s="2" t="n">
+      <c r="E142" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F142" s="2" t="n">
+      <c r="F142" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G142" s="3">
+      <c r="G142" s="5">
         <f>IF(AND(E142&lt;&gt;"",F142&lt;&gt;""),F142-E142,"")</f>
         <v/>
       </c>
@@ -7153,13 +7154,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E143" s="2" t="n">
+      <c r="E143" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F143" s="2" t="n">
+      <c r="F143" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G143" s="3">
+      <c r="G143" s="5">
         <f>IF(AND(E143&lt;&gt;"",F143&lt;&gt;""),F143-E143,"")</f>
         <v/>
       </c>
@@ -7205,13 +7206,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E144" s="2" t="n">
+      <c r="E144" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F144" s="2" t="n">
+      <c r="F144" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G144" s="3">
+      <c r="G144" s="5">
         <f>IF(AND(E144&lt;&gt;"",F144&lt;&gt;""),F144-E144,"")</f>
         <v/>
       </c>
@@ -7257,13 +7258,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E145" s="2" t="n">
+      <c r="E145" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F145" s="2" t="n">
+      <c r="F145" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G145" s="3">
+      <c r="G145" s="5">
         <f>IF(AND(E145&lt;&gt;"",F145&lt;&gt;""),F145-E145,"")</f>
         <v/>
       </c>
@@ -7309,13 +7310,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E146" s="2" t="n">
+      <c r="E146" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F146" s="2" t="n">
+      <c r="F146" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G146" s="3">
+      <c r="G146" s="5">
         <f>IF(AND(E146&lt;&gt;"",F146&lt;&gt;""),F146-E146,"")</f>
         <v/>
       </c>
@@ -7361,13 +7362,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E147" s="2" t="n">
+      <c r="E147" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F147" s="2" t="n">
+      <c r="F147" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G147" s="3">
+      <c r="G147" s="5">
         <f>IF(AND(E147&lt;&gt;"",F147&lt;&gt;""),F147-E147,"")</f>
         <v/>
       </c>
@@ -7413,13 +7414,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E148" s="2" t="n">
+      <c r="E148" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F148" s="2" t="n">
+      <c r="F148" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G148" s="3">
+      <c r="G148" s="5">
         <f>IF(AND(E148&lt;&gt;"",F148&lt;&gt;""),F148-E148,"")</f>
         <v/>
       </c>
@@ -7465,13 +7466,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E149" s="2" t="n">
+      <c r="E149" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F149" s="2" t="n">
+      <c r="F149" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G149" s="3">
+      <c r="G149" s="5">
         <f>IF(AND(E149&lt;&gt;"",F149&lt;&gt;""),F149-E149,"")</f>
         <v/>
       </c>
@@ -7517,13 +7518,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E150" s="2" t="n">
+      <c r="E150" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F150" s="2" t="n">
+      <c r="F150" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G150" s="3">
+      <c r="G150" s="5">
         <f>IF(AND(E150&lt;&gt;"",F150&lt;&gt;""),F150-E150,"")</f>
         <v/>
       </c>
@@ -7569,13 +7570,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E151" s="2" t="n">
+      <c r="E151" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F151" s="2" t="n">
+      <c r="F151" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G151" s="3">
+      <c r="G151" s="5">
         <f>IF(AND(E151&lt;&gt;"",F151&lt;&gt;""),F151-E151,"")</f>
         <v/>
       </c>
@@ -7621,13 +7622,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E152" s="2" t="n">
+      <c r="E152" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F152" s="2" t="n">
+      <c r="F152" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G152" s="3">
+      <c r="G152" s="5">
         <f>IF(AND(E152&lt;&gt;"",F152&lt;&gt;""),F152-E152,"")</f>
         <v/>
       </c>
@@ -7673,13 +7674,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E153" s="2" t="n">
+      <c r="E153" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F153" s="2" t="n">
+      <c r="F153" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G153" s="3">
+      <c r="G153" s="5">
         <f>IF(AND(E153&lt;&gt;"",F153&lt;&gt;""),F153-E153,"")</f>
         <v/>
       </c>
@@ -7725,13 +7726,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E154" s="2" t="n">
+      <c r="E154" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F154" s="2" t="n">
+      <c r="F154" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G154" s="3">
+      <c r="G154" s="5">
         <f>IF(AND(E154&lt;&gt;"",F154&lt;&gt;""),F154-E154,"")</f>
         <v/>
       </c>
@@ -7777,13 +7778,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E155" s="2" t="n">
+      <c r="E155" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F155" s="2" t="n">
+      <c r="F155" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G155" s="3">
+      <c r="G155" s="5">
         <f>IF(AND(E155&lt;&gt;"",F155&lt;&gt;""),F155-E155,"")</f>
         <v/>
       </c>
@@ -7829,13 +7830,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E156" s="2" t="n">
+      <c r="E156" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F156" s="2" t="n">
+      <c r="F156" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G156" s="3">
+      <c r="G156" s="5">
         <f>IF(AND(E156&lt;&gt;"",F156&lt;&gt;""),F156-E156,"")</f>
         <v/>
       </c>
@@ -7881,13 +7882,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E157" s="2" t="n">
+      <c r="E157" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F157" s="2" t="n">
+      <c r="F157" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G157" s="3">
+      <c r="G157" s="5">
         <f>IF(AND(E157&lt;&gt;"",F157&lt;&gt;""),F157-E157,"")</f>
         <v/>
       </c>
@@ -7933,13 +7934,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E158" s="2" t="n">
+      <c r="E158" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F158" s="2" t="n">
+      <c r="F158" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G158" s="3">
+      <c r="G158" s="5">
         <f>IF(AND(E158&lt;&gt;"",F158&lt;&gt;""),F158-E158,"")</f>
         <v/>
       </c>
@@ -7985,13 +7986,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E159" s="2" t="n">
+      <c r="E159" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F159" s="2" t="n">
+      <c r="F159" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G159" s="3">
+      <c r="G159" s="5">
         <f>IF(AND(E159&lt;&gt;"",F159&lt;&gt;""),F159-E159,"")</f>
         <v/>
       </c>
@@ -8037,13 +8038,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E160" s="2" t="n">
+      <c r="E160" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F160" s="2" t="n">
+      <c r="F160" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G160" s="3">
+      <c r="G160" s="5">
         <f>IF(AND(E160&lt;&gt;"",F160&lt;&gt;""),F160-E160,"")</f>
         <v/>
       </c>
@@ -8089,13 +8090,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E161" s="2" t="n">
+      <c r="E161" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F161" s="2" t="n">
+      <c r="F161" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G161" s="3">
+      <c r="G161" s="5">
         <f>IF(AND(E161&lt;&gt;"",F161&lt;&gt;""),F161-E161,"")</f>
         <v/>
       </c>
@@ -8141,13 +8142,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E162" s="2" t="n">
+      <c r="E162" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F162" s="2" t="n">
+      <c r="F162" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G162" s="3">
+      <c r="G162" s="5">
         <f>IF(AND(E162&lt;&gt;"",F162&lt;&gt;""),F162-E162,"")</f>
         <v/>
       </c>
@@ -8193,13 +8194,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E163" s="2" t="n">
+      <c r="E163" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F163" s="2" t="n">
+      <c r="F163" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G163" s="3">
+      <c r="G163" s="5">
         <f>IF(AND(E163&lt;&gt;"",F163&lt;&gt;""),F163-E163,"")</f>
         <v/>
       </c>
@@ -8245,13 +8246,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E164" s="2" t="n">
+      <c r="E164" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F164" s="2" t="n">
+      <c r="F164" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G164" s="3">
+      <c r="G164" s="5">
         <f>IF(AND(E164&lt;&gt;"",F164&lt;&gt;""),F164-E164,"")</f>
         <v/>
       </c>
@@ -8297,13 +8298,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E165" s="2" t="n">
+      <c r="E165" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F165" s="2" t="n">
+      <c r="F165" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G165" s="3">
+      <c r="G165" s="5">
         <f>IF(AND(E165&lt;&gt;"",F165&lt;&gt;""),F165-E165,"")</f>
         <v/>
       </c>
@@ -8349,13 +8350,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E166" s="2" t="n">
+      <c r="E166" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F166" s="2" t="n">
+      <c r="F166" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G166" s="3">
+      <c r="G166" s="5">
         <f>IF(AND(E166&lt;&gt;"",F166&lt;&gt;""),F166-E166,"")</f>
         <v/>
       </c>
@@ -8401,13 +8402,13 @@
           <t>Service interruption of 17 (2G)(4G) xD and 11 (2G)(4G) xC sites at certain parts of Serian 1, Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E167" s="2" t="n">
+      <c r="E167" s="4" t="n">
         <v>46216.53263888889</v>
       </c>
-      <c r="F167" s="2" t="n">
+      <c r="F167" s="4" t="n">
         <v>46216.67222222222</v>
       </c>
-      <c r="G167" s="3">
+      <c r="G167" s="5">
         <f>IF(AND(E167&lt;&gt;"",F167&lt;&gt;""),F167-E167,"")</f>
         <v/>
       </c>
@@ -8453,13 +8454,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E168" s="2" t="n">
+      <c r="E168" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F168" s="2" t="n">
+      <c r="F168" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G168" s="3">
+      <c r="G168" s="5">
         <f>IF(AND(E168&lt;&gt;"",F168&lt;&gt;""),F168-E168,"")</f>
         <v/>
       </c>
@@ -8505,13 +8506,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E169" s="2" t="n">
+      <c r="E169" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F169" s="2" t="n">
+      <c r="F169" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G169" s="3">
+      <c r="G169" s="5">
         <f>IF(AND(E169&lt;&gt;"",F169&lt;&gt;""),F169-E169,"")</f>
         <v/>
       </c>
@@ -8557,13 +8558,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E170" s="2" t="n">
+      <c r="E170" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F170" s="2" t="n">
+      <c r="F170" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G170" s="3">
+      <c r="G170" s="5">
         <f>IF(AND(E170&lt;&gt;"",F170&lt;&gt;""),F170-E170,"")</f>
         <v/>
       </c>
@@ -8609,13 +8610,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E171" s="2" t="n">
+      <c r="E171" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F171" s="2" t="n">
+      <c r="F171" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G171" s="3">
+      <c r="G171" s="5">
         <f>IF(AND(E171&lt;&gt;"",F171&lt;&gt;""),F171-E171,"")</f>
         <v/>
       </c>
@@ -8661,13 +8662,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E172" s="2" t="n">
+      <c r="E172" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F172" s="2" t="n">
+      <c r="F172" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G172" s="3">
+      <c r="G172" s="5">
         <f>IF(AND(E172&lt;&gt;"",F172&lt;&gt;""),F172-E172,"")</f>
         <v/>
       </c>
@@ -8713,13 +8714,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E173" s="2" t="n">
+      <c r="E173" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F173" s="2" t="n">
+      <c r="F173" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G173" s="3">
+      <c r="G173" s="5">
         <f>IF(AND(E173&lt;&gt;"",F173&lt;&gt;""),F173-E173,"")</f>
         <v/>
       </c>
@@ -8765,13 +8766,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E174" s="2" t="n">
+      <c r="E174" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F174" s="2" t="n">
+      <c r="F174" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G174" s="3">
+      <c r="G174" s="5">
         <f>IF(AND(E174&lt;&gt;"",F174&lt;&gt;""),F174-E174,"")</f>
         <v/>
       </c>
@@ -8817,13 +8818,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E175" s="2" t="n">
+      <c r="E175" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F175" s="2" t="n">
+      <c r="F175" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G175" s="3">
+      <c r="G175" s="5">
         <f>IF(AND(E175&lt;&gt;"",F175&lt;&gt;""),F175-E175,"")</f>
         <v/>
       </c>
@@ -8869,13 +8870,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E176" s="2" t="n">
+      <c r="E176" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F176" s="2" t="n">
+      <c r="F176" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G176" s="3">
+      <c r="G176" s="5">
         <f>IF(AND(E176&lt;&gt;"",F176&lt;&gt;""),F176-E176,"")</f>
         <v/>
       </c>
@@ -8921,13 +8922,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E177" s="2" t="n">
+      <c r="E177" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F177" s="2" t="n">
+      <c r="F177" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G177" s="3">
+      <c r="G177" s="5">
         <f>IF(AND(E177&lt;&gt;"",F177&lt;&gt;""),F177-E177,"")</f>
         <v/>
       </c>
@@ -8973,13 +8974,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E178" s="2" t="n">
+      <c r="E178" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F178" s="2" t="n">
+      <c r="F178" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G178" s="3">
+      <c r="G178" s="5">
         <f>IF(AND(E178&lt;&gt;"",F178&lt;&gt;""),F178-E178,"")</f>
         <v/>
       </c>
@@ -9025,13 +9026,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E179" s="2" t="n">
+      <c r="E179" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F179" s="2" t="n">
+      <c r="F179" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G179" s="3">
+      <c r="G179" s="5">
         <f>IF(AND(E179&lt;&gt;"",F179&lt;&gt;""),F179-E179,"")</f>
         <v/>
       </c>
@@ -9077,13 +9078,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E180" s="2" t="n">
+      <c r="E180" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F180" s="2" t="n">
+      <c r="F180" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G180" s="3">
+      <c r="G180" s="5">
         <f>IF(AND(E180&lt;&gt;"",F180&lt;&gt;""),F180-E180,"")</f>
         <v/>
       </c>
@@ -9129,13 +9130,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E181" s="2" t="n">
+      <c r="E181" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F181" s="2" t="n">
+      <c r="F181" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G181" s="3">
+      <c r="G181" s="5">
         <f>IF(AND(E181&lt;&gt;"",F181&lt;&gt;""),F181-E181,"")</f>
         <v/>
       </c>
@@ -9181,13 +9182,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E182" s="2" t="n">
+      <c r="E182" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F182" s="2" t="n">
+      <c r="F182" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G182" s="3">
+      <c r="G182" s="5">
         <f>IF(AND(E182&lt;&gt;"",F182&lt;&gt;""),F182-E182,"")</f>
         <v/>
       </c>
@@ -9233,13 +9234,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E183" s="2" t="n">
+      <c r="E183" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F183" s="2" t="n">
+      <c r="F183" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G183" s="3">
+      <c r="G183" s="5">
         <f>IF(AND(E183&lt;&gt;"",F183&lt;&gt;""),F183-E183,"")</f>
         <v/>
       </c>
@@ -9285,13 +9286,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E184" s="2" t="n">
+      <c r="E184" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F184" s="2" t="n">
+      <c r="F184" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G184" s="3">
+      <c r="G184" s="5">
         <f>IF(AND(E184&lt;&gt;"",F184&lt;&gt;""),F184-E184,"")</f>
         <v/>
       </c>
@@ -9337,13 +9338,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E185" s="2" t="n">
+      <c r="E185" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F185" s="2" t="n">
+      <c r="F185" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G185" s="3">
+      <c r="G185" s="5">
         <f>IF(AND(E185&lt;&gt;"",F185&lt;&gt;""),F185-E185,"")</f>
         <v/>
       </c>
@@ -9389,13 +9390,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E186" s="2" t="n">
+      <c r="E186" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F186" s="2" t="n">
+      <c r="F186" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G186" s="3">
+      <c r="G186" s="5">
         <f>IF(AND(E186&lt;&gt;"",F186&lt;&gt;""),F186-E186,"")</f>
         <v/>
       </c>
@@ -9441,13 +9442,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E187" s="2" t="n">
+      <c r="E187" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F187" s="2" t="n">
+      <c r="F187" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G187" s="3">
+      <c r="G187" s="5">
         <f>IF(AND(E187&lt;&gt;"",F187&lt;&gt;""),F187-E187,"")</f>
         <v/>
       </c>
@@ -9493,13 +9494,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan, Kunak, Lahad Datu-Felda Sahabat area, Sabah</t>
         </is>
       </c>
-      <c r="E188" s="2" t="n">
+      <c r="E188" s="4" t="n">
         <v>46216.45486111111</v>
       </c>
-      <c r="F188" s="2" t="n">
+      <c r="F188" s="4" t="n">
         <v>46216.47986111111</v>
       </c>
-      <c r="G188" s="3">
+      <c r="G188" s="5">
         <f>IF(AND(E188&lt;&gt;"",F188&lt;&gt;""),F188-E188,"")</f>
         <v/>
       </c>
@@ -9545,10 +9546,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E189" s="2" t="n">
+      <c r="E189" s="4" t="n">
         <v>46216.45138888889</v>
       </c>
-      <c r="G189" s="3">
+      <c r="G189" s="5">
         <f>IF(AND(E189&lt;&gt;"",F189&lt;&gt;""),F189-E189,"")</f>
         <v/>
       </c>
@@ -9584,10 +9585,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E190" s="2" t="n">
+      <c r="E190" s="4" t="n">
         <v>46216.45138888889</v>
       </c>
-      <c r="G190" s="3">
+      <c r="G190" s="5">
         <f>IF(AND(E190&lt;&gt;"",F190&lt;&gt;""),F190-E190,"")</f>
         <v/>
       </c>
@@ -9623,10 +9624,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E191" s="2" t="n">
+      <c r="E191" s="4" t="n">
         <v>46216.45138888889</v>
       </c>
-      <c r="G191" s="3">
+      <c r="G191" s="5">
         <f>IF(AND(E191&lt;&gt;"",F191&lt;&gt;""),F191-E191,"")</f>
         <v/>
       </c>
@@ -9662,10 +9663,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E192" s="2" t="n">
+      <c r="E192" s="4" t="n">
         <v>46216.45138888889</v>
       </c>
-      <c r="G192" s="3">
+      <c r="G192" s="5">
         <f>IF(AND(E192&lt;&gt;"",F192&lt;&gt;""),F192-E192,"")</f>
         <v/>
       </c>
@@ -9701,10 +9702,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Mile 10 To 20 area, Sarawak</t>
         </is>
       </c>
-      <c r="E193" s="2" t="n">
+      <c r="E193" s="4" t="n">
         <v>46216.45138888889</v>
       </c>
-      <c r="G193" s="3">
+      <c r="G193" s="5">
         <f>IF(AND(E193&lt;&gt;"",F193&lt;&gt;""),F193-E193,"")</f>
         <v/>
       </c>
@@ -9740,10 +9741,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 3 (2G)(4G) xC sites at certain parts of Lahad Datu-Felda Sahabat, Lahad Datu-Fajar area, Sabah</t>
         </is>
       </c>
-      <c r="E194" s="2" t="n">
+      <c r="E194" s="4" t="n">
         <v>46216.42708333334</v>
       </c>
-      <c r="G194" s="3">
+      <c r="G194" s="5">
         <f>IF(AND(E194&lt;&gt;"",F194&lt;&gt;""),F194-E194,"")</f>
         <v/>
       </c>
@@ -9779,10 +9780,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 3 (2G)(4G) xC sites at certain parts of Lahad Datu-Felda Sahabat, Lahad Datu-Fajar area, Sabah</t>
         </is>
       </c>
-      <c r="E195" s="2" t="n">
+      <c r="E195" s="4" t="n">
         <v>46216.42708333334</v>
       </c>
-      <c r="G195" s="3">
+      <c r="G195" s="5">
         <f>IF(AND(E195&lt;&gt;"",F195&lt;&gt;""),F195-E195,"")</f>
         <v/>
       </c>
@@ -9818,10 +9819,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 3 (2G)(4G) xC sites at certain parts of Lahad Datu-Felda Sahabat, Lahad Datu-Fajar area, Sabah</t>
         </is>
       </c>
-      <c r="E196" s="2" t="n">
+      <c r="E196" s="4" t="n">
         <v>46216.42708333334</v>
       </c>
-      <c r="G196" s="3">
+      <c r="G196" s="5">
         <f>IF(AND(E196&lt;&gt;"",F196&lt;&gt;""),F196-E196,"")</f>
         <v/>
       </c>
@@ -9857,10 +9858,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 3 (2G)(4G) xC sites at certain parts of Lahad Datu-Felda Sahabat, Lahad Datu-Fajar area, Sabah</t>
         </is>
       </c>
-      <c r="E197" s="2" t="n">
+      <c r="E197" s="4" t="n">
         <v>46216.42708333334</v>
       </c>
-      <c r="G197" s="3">
+      <c r="G197" s="5">
         <f>IF(AND(E197&lt;&gt;"",F197&lt;&gt;""),F197-E197,"")</f>
         <v/>
       </c>
@@ -9896,10 +9897,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 3 (2G)(4G) xC sites at certain parts of Lahad Datu-Felda Sahabat, Lahad Datu-Fajar area, Sabah</t>
         </is>
       </c>
-      <c r="E198" s="2" t="n">
+      <c r="E198" s="4" t="n">
         <v>46216.42708333334</v>
       </c>
-      <c r="G198" s="3">
+      <c r="G198" s="5">
         <f>IF(AND(E198&lt;&gt;"",F198&lt;&gt;""),F198-E198,"")</f>
         <v/>
       </c>
@@ -9935,10 +9936,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Serian 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E199" s="2" t="n">
+      <c r="E199" s="4" t="n">
         <v>46216.39791666667</v>
       </c>
-      <c r="G199" s="3">
+      <c r="G199" s="5">
         <f>IF(AND(E199&lt;&gt;"",F199&lt;&gt;""),F199-E199,"")</f>
         <v/>
       </c>
@@ -9974,10 +9975,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Serian 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E200" s="2" t="n">
+      <c r="E200" s="4" t="n">
         <v>46216.39791666667</v>
       </c>
-      <c r="G200" s="3">
+      <c r="G200" s="5">
         <f>IF(AND(E200&lt;&gt;"",F200&lt;&gt;""),F200-E200,"")</f>
         <v/>
       </c>
@@ -10013,10 +10014,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Serian 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E201" s="2" t="n">
+      <c r="E201" s="4" t="n">
         <v>46216.39791666667</v>
       </c>
-      <c r="G201" s="3">
+      <c r="G201" s="5">
         <f>IF(AND(E201&lt;&gt;"",F201&lt;&gt;""),F201-E201,"")</f>
         <v/>
       </c>
@@ -10052,10 +10053,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Serian 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E202" s="2" t="n">
+      <c r="E202" s="4" t="n">
         <v>46216.39791666667</v>
       </c>
-      <c r="G202" s="3">
+      <c r="G202" s="5">
         <f>IF(AND(E202&lt;&gt;"",F202&lt;&gt;""),F202-E202,"")</f>
         <v/>
       </c>
@@ -10091,10 +10092,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Serian 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E203" s="2" t="n">
+      <c r="E203" s="4" t="n">
         <v>46216.39791666667</v>
       </c>
-      <c r="G203" s="3">
+      <c r="G203" s="5">
         <f>IF(AND(E203&lt;&gt;"",F203&lt;&gt;""),F203-E203,"")</f>
         <v/>
       </c>
@@ -10130,10 +10131,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Serian 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E204" s="2" t="n">
+      <c r="E204" s="4" t="n">
         <v>46216.39791666667</v>
       </c>
-      <c r="G204" s="3">
+      <c r="G204" s="5">
         <f>IF(AND(E204&lt;&gt;"",F204&lt;&gt;""),F204-E204,"")</f>
         <v/>
       </c>
@@ -10169,10 +10170,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Serian 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E205" s="2" t="n">
+      <c r="E205" s="4" t="n">
         <v>46216.39791666667</v>
       </c>
-      <c r="G205" s="3">
+      <c r="G205" s="5">
         <f>IF(AND(E205&lt;&gt;"",F205&lt;&gt;""),F205-E205,"")</f>
         <v/>
       </c>
@@ -10208,10 +10209,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Serian 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E206" s="2" t="n">
+      <c r="E206" s="4" t="n">
         <v>46216.39791666667</v>
       </c>
-      <c r="G206" s="3">
+      <c r="G206" s="5">
         <f>IF(AND(E206&lt;&gt;"",F206&lt;&gt;""),F206-E206,"")</f>
         <v/>
       </c>
@@ -10247,13 +10248,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E207" s="2" t="n">
+      <c r="E207" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F207" s="2" t="n">
+      <c r="F207" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G207" s="3">
+      <c r="G207" s="5">
         <f>IF(AND(E207&lt;&gt;"",F207&lt;&gt;""),F207-E207,"")</f>
         <v/>
       </c>
@@ -10299,13 +10300,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E208" s="2" t="n">
+      <c r="E208" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F208" s="2" t="n">
+      <c r="F208" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G208" s="3">
+      <c r="G208" s="5">
         <f>IF(AND(E208&lt;&gt;"",F208&lt;&gt;""),F208-E208,"")</f>
         <v/>
       </c>
@@ -10351,13 +10352,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E209" s="2" t="n">
+      <c r="E209" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F209" s="2" t="n">
+      <c r="F209" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G209" s="3">
+      <c r="G209" s="5">
         <f>IF(AND(E209&lt;&gt;"",F209&lt;&gt;""),F209-E209,"")</f>
         <v/>
       </c>
@@ -10403,13 +10404,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E210" s="2" t="n">
+      <c r="E210" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F210" s="2" t="n">
+      <c r="F210" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G210" s="3">
+      <c r="G210" s="5">
         <f>IF(AND(E210&lt;&gt;"",F210&lt;&gt;""),F210-E210,"")</f>
         <v/>
       </c>
@@ -10455,13 +10456,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E211" s="2" t="n">
+      <c r="E211" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F211" s="2" t="n">
+      <c r="F211" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G211" s="3">
+      <c r="G211" s="5">
         <f>IF(AND(E211&lt;&gt;"",F211&lt;&gt;""),F211-E211,"")</f>
         <v/>
       </c>
@@ -10507,13 +10508,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E212" s="2" t="n">
+      <c r="E212" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F212" s="2" t="n">
+      <c r="F212" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G212" s="3">
+      <c r="G212" s="5">
         <f>IF(AND(E212&lt;&gt;"",F212&lt;&gt;""),F212-E212,"")</f>
         <v/>
       </c>
@@ -10559,13 +10560,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E213" s="2" t="n">
+      <c r="E213" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F213" s="2" t="n">
+      <c r="F213" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G213" s="3">
+      <c r="G213" s="5">
         <f>IF(AND(E213&lt;&gt;"",F213&lt;&gt;""),F213-E213,"")</f>
         <v/>
       </c>
@@ -10611,13 +10612,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E214" s="2" t="n">
+      <c r="E214" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F214" s="2" t="n">
+      <c r="F214" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G214" s="3">
+      <c r="G214" s="5">
         <f>IF(AND(E214&lt;&gt;"",F214&lt;&gt;""),F214-E214,"")</f>
         <v/>
       </c>
@@ -10663,13 +10664,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E215" s="2" t="n">
+      <c r="E215" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F215" s="2" t="n">
+      <c r="F215" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G215" s="3">
+      <c r="G215" s="5">
         <f>IF(AND(E215&lt;&gt;"",F215&lt;&gt;""),F215-E215,"")</f>
         <v/>
       </c>
@@ -10715,13 +10716,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E216" s="2" t="n">
+      <c r="E216" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F216" s="2" t="n">
+      <c r="F216" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G216" s="3">
+      <c r="G216" s="5">
         <f>IF(AND(E216&lt;&gt;"",F216&lt;&gt;""),F216-E216,"")</f>
         <v/>
       </c>
@@ -10767,13 +10768,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E217" s="2" t="n">
+      <c r="E217" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F217" s="2" t="n">
+      <c r="F217" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G217" s="3">
+      <c r="G217" s="5">
         <f>IF(AND(E217&lt;&gt;"",F217&lt;&gt;""),F217-E217,"")</f>
         <v/>
       </c>
@@ -10819,13 +10820,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E218" s="2" t="n">
+      <c r="E218" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F218" s="2" t="n">
+      <c r="F218" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G218" s="3">
+      <c r="G218" s="5">
         <f>IF(AND(E218&lt;&gt;"",F218&lt;&gt;""),F218-E218,"")</f>
         <v/>
       </c>
@@ -10871,13 +10872,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E219" s="2" t="n">
+      <c r="E219" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F219" s="2" t="n">
+      <c r="F219" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G219" s="3">
+      <c r="G219" s="5">
         <f>IF(AND(E219&lt;&gt;"",F219&lt;&gt;""),F219-E219,"")</f>
         <v/>
       </c>
@@ -10923,13 +10924,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E220" s="2" t="n">
+      <c r="E220" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F220" s="2" t="n">
+      <c r="F220" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G220" s="3">
+      <c r="G220" s="5">
         <f>IF(AND(E220&lt;&gt;"",F220&lt;&gt;""),F220-E220,"")</f>
         <v/>
       </c>
@@ -10975,13 +10976,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E221" s="2" t="n">
+      <c r="E221" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F221" s="2" t="n">
+      <c r="F221" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G221" s="3">
+      <c r="G221" s="5">
         <f>IF(AND(E221&lt;&gt;"",F221&lt;&gt;""),F221-E221,"")</f>
         <v/>
       </c>
@@ -11027,13 +11028,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E222" s="2" t="n">
+      <c r="E222" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F222" s="2" t="n">
+      <c r="F222" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G222" s="3">
+      <c r="G222" s="5">
         <f>IF(AND(E222&lt;&gt;"",F222&lt;&gt;""),F222-E222,"")</f>
         <v/>
       </c>
@@ -11079,13 +11080,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E223" s="2" t="n">
+      <c r="E223" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F223" s="2" t="n">
+      <c r="F223" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G223" s="3">
+      <c r="G223" s="5">
         <f>IF(AND(E223&lt;&gt;"",F223&lt;&gt;""),F223-E223,"")</f>
         <v/>
       </c>
@@ -11131,13 +11132,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E224" s="2" t="n">
+      <c r="E224" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F224" s="2" t="n">
+      <c r="F224" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G224" s="3">
+      <c r="G224" s="5">
         <f>IF(AND(E224&lt;&gt;"",F224&lt;&gt;""),F224-E224,"")</f>
         <v/>
       </c>
@@ -11183,13 +11184,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E225" s="2" t="n">
+      <c r="E225" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F225" s="2" t="n">
+      <c r="F225" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G225" s="3">
+      <c r="G225" s="5">
         <f>IF(AND(E225&lt;&gt;"",F225&lt;&gt;""),F225-E225,"")</f>
         <v/>
       </c>
@@ -11235,13 +11236,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E226" s="2" t="n">
+      <c r="E226" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F226" s="2" t="n">
+      <c r="F226" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G226" s="3">
+      <c r="G226" s="5">
         <f>IF(AND(E226&lt;&gt;"",F226&lt;&gt;""),F226-E226,"")</f>
         <v/>
       </c>
@@ -11287,13 +11288,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E227" s="2" t="n">
+      <c r="E227" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F227" s="2" t="n">
+      <c r="F227" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G227" s="3">
+      <c r="G227" s="5">
         <f>IF(AND(E227&lt;&gt;"",F227&lt;&gt;""),F227-E227,"")</f>
         <v/>
       </c>
@@ -11339,13 +11340,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E228" s="2" t="n">
+      <c r="E228" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F228" s="2" t="n">
+      <c r="F228" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G228" s="3">
+      <c r="G228" s="5">
         <f>IF(AND(E228&lt;&gt;"",F228&lt;&gt;""),F228-E228,"")</f>
         <v/>
       </c>
@@ -11391,13 +11392,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E229" s="2" t="n">
+      <c r="E229" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F229" s="2" t="n">
+      <c r="F229" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G229" s="3">
+      <c r="G229" s="5">
         <f>IF(AND(E229&lt;&gt;"",F229&lt;&gt;""),F229-E229,"")</f>
         <v/>
       </c>
@@ -11443,13 +11444,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E230" s="2" t="n">
+      <c r="E230" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F230" s="2" t="n">
+      <c r="F230" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G230" s="3">
+      <c r="G230" s="5">
         <f>IF(AND(E230&lt;&gt;"",F230&lt;&gt;""),F230-E230,"")</f>
         <v/>
       </c>
@@ -11495,13 +11496,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E231" s="2" t="n">
+      <c r="E231" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F231" s="2" t="n">
+      <c r="F231" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G231" s="3">
+      <c r="G231" s="5">
         <f>IF(AND(E231&lt;&gt;"",F231&lt;&gt;""),F231-E231,"")</f>
         <v/>
       </c>
@@ -11547,13 +11548,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E232" s="2" t="n">
+      <c r="E232" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F232" s="2" t="n">
+      <c r="F232" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G232" s="3">
+      <c r="G232" s="5">
         <f>IF(AND(E232&lt;&gt;"",F232&lt;&gt;""),F232-E232,"")</f>
         <v/>
       </c>
@@ -11599,13 +11600,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E233" s="2" t="n">
+      <c r="E233" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F233" s="2" t="n">
+      <c r="F233" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G233" s="3">
+      <c r="G233" s="5">
         <f>IF(AND(E233&lt;&gt;"",F233&lt;&gt;""),F233-E233,"")</f>
         <v/>
       </c>
@@ -11651,13 +11652,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E234" s="2" t="n">
+      <c r="E234" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F234" s="2" t="n">
+      <c r="F234" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G234" s="3">
+      <c r="G234" s="5">
         <f>IF(AND(E234&lt;&gt;"",F234&lt;&gt;""),F234-E234,"")</f>
         <v/>
       </c>
@@ -11703,13 +11704,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E235" s="2" t="n">
+      <c r="E235" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F235" s="2" t="n">
+      <c r="F235" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G235" s="3">
+      <c r="G235" s="5">
         <f>IF(AND(E235&lt;&gt;"",F235&lt;&gt;""),F235-E235,"")</f>
         <v/>
       </c>
@@ -11755,13 +11756,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E236" s="2" t="n">
+      <c r="E236" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F236" s="2" t="n">
+      <c r="F236" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G236" s="3">
+      <c r="G236" s="5">
         <f>IF(AND(E236&lt;&gt;"",F236&lt;&gt;""),F236-E236,"")</f>
         <v/>
       </c>
@@ -11807,13 +11808,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E237" s="2" t="n">
+      <c r="E237" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F237" s="2" t="n">
+      <c r="F237" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G237" s="3">
+      <c r="G237" s="5">
         <f>IF(AND(E237&lt;&gt;"",F237&lt;&gt;""),F237-E237,"")</f>
         <v/>
       </c>
@@ -11859,13 +11860,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E238" s="2" t="n">
+      <c r="E238" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F238" s="2" t="n">
+      <c r="F238" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G238" s="3">
+      <c r="G238" s="5">
         <f>IF(AND(E238&lt;&gt;"",F238&lt;&gt;""),F238-E238,"")</f>
         <v/>
       </c>
@@ -11911,13 +11912,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E239" s="2" t="n">
+      <c r="E239" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F239" s="2" t="n">
+      <c r="F239" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G239" s="3">
+      <c r="G239" s="5">
         <f>IF(AND(E239&lt;&gt;"",F239&lt;&gt;""),F239-E239,"")</f>
         <v/>
       </c>
@@ -11963,13 +11964,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E240" s="2" t="n">
+      <c r="E240" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F240" s="2" t="n">
+      <c r="F240" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G240" s="3">
+      <c r="G240" s="5">
         <f>IF(AND(E240&lt;&gt;"",F240&lt;&gt;""),F240-E240,"")</f>
         <v/>
       </c>
@@ -12015,13 +12016,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E241" s="2" t="n">
+      <c r="E241" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F241" s="2" t="n">
+      <c r="F241" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G241" s="3">
+      <c r="G241" s="5">
         <f>IF(AND(E241&lt;&gt;"",F241&lt;&gt;""),F241-E241,"")</f>
         <v/>
       </c>
@@ -12067,13 +12068,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E242" s="2" t="n">
+      <c r="E242" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F242" s="2" t="n">
+      <c r="F242" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G242" s="3">
+      <c r="G242" s="5">
         <f>IF(AND(E242&lt;&gt;"",F242&lt;&gt;""),F242-E242,"")</f>
         <v/>
       </c>
@@ -12119,13 +12120,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E243" s="2" t="n">
+      <c r="E243" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F243" s="2" t="n">
+      <c r="F243" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G243" s="3">
+      <c r="G243" s="5">
         <f>IF(AND(E243&lt;&gt;"",F243&lt;&gt;""),F243-E243,"")</f>
         <v/>
       </c>
@@ -12171,13 +12172,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E244" s="2" t="n">
+      <c r="E244" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F244" s="2" t="n">
+      <c r="F244" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G244" s="3">
+      <c r="G244" s="5">
         <f>IF(AND(E244&lt;&gt;"",F244&lt;&gt;""),F244-E244,"")</f>
         <v/>
       </c>
@@ -12223,13 +12224,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E245" s="2" t="n">
+      <c r="E245" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F245" s="2" t="n">
+      <c r="F245" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G245" s="3">
+      <c r="G245" s="5">
         <f>IF(AND(E245&lt;&gt;"",F245&lt;&gt;""),F245-E245,"")</f>
         <v/>
       </c>
@@ -12275,13 +12276,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E246" s="2" t="n">
+      <c r="E246" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F246" s="2" t="n">
+      <c r="F246" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G246" s="3">
+      <c r="G246" s="5">
         <f>IF(AND(E246&lt;&gt;"",F246&lt;&gt;""),F246-E246,"")</f>
         <v/>
       </c>
@@ -12327,13 +12328,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E247" s="2" t="n">
+      <c r="E247" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F247" s="2" t="n">
+      <c r="F247" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G247" s="3">
+      <c r="G247" s="5">
         <f>IF(AND(E247&lt;&gt;"",F247&lt;&gt;""),F247-E247,"")</f>
         <v/>
       </c>
@@ -12379,13 +12380,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E248" s="2" t="n">
+      <c r="E248" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F248" s="2" t="n">
+      <c r="F248" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G248" s="3">
+      <c r="G248" s="5">
         <f>IF(AND(E248&lt;&gt;"",F248&lt;&gt;""),F248-E248,"")</f>
         <v/>
       </c>
@@ -12431,13 +12432,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E249" s="2" t="n">
+      <c r="E249" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F249" s="2" t="n">
+      <c r="F249" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G249" s="3">
+      <c r="G249" s="5">
         <f>IF(AND(E249&lt;&gt;"",F249&lt;&gt;""),F249-E249,"")</f>
         <v/>
       </c>
@@ -12483,13 +12484,13 @@
           <t>Service interruption of 29 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Serian 1, Sri Aman / Betong 1, Sarikei / Kanowit 2, Sri Aman / Betong area, Sarawak</t>
         </is>
       </c>
-      <c r="E250" s="2" t="n">
+      <c r="E250" s="4" t="n">
         <v>46216.37777777778</v>
       </c>
-      <c r="F250" s="2" t="n">
+      <c r="F250" s="4" t="n">
         <v>46216.65625</v>
       </c>
-      <c r="G250" s="3">
+      <c r="G250" s="5">
         <f>IF(AND(E250&lt;&gt;"",F250&lt;&gt;""),F250-E250,"")</f>
         <v/>
       </c>
@@ -12535,10 +12536,10 @@
           <t>Service interruption of 8 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Rawang 1, Batang Kali / Kuala Kubu Baru area, Selangor</t>
         </is>
       </c>
-      <c r="E251" s="2" t="n">
+      <c r="E251" s="4" t="n">
         <v>46216.35833333333</v>
       </c>
-      <c r="G251" s="3">
+      <c r="G251" s="5">
         <f>IF(AND(E251&lt;&gt;"",F251&lt;&gt;""),F251-E251,"")</f>
         <v/>
       </c>
@@ -12574,10 +12575,10 @@
           <t>Service interruption of 8 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Rawang 1, Batang Kali / Kuala Kubu Baru area, Selangor</t>
         </is>
       </c>
-      <c r="E252" s="2" t="n">
+      <c r="E252" s="4" t="n">
         <v>46216.35833333333</v>
       </c>
-      <c r="G252" s="3">
+      <c r="G252" s="5">
         <f>IF(AND(E252&lt;&gt;"",F252&lt;&gt;""),F252-E252,"")</f>
         <v/>
       </c>
@@ -12613,10 +12614,10 @@
           <t>Service interruption of 8 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Rawang 1, Batang Kali / Kuala Kubu Baru area, Selangor</t>
         </is>
       </c>
-      <c r="E253" s="2" t="n">
+      <c r="E253" s="4" t="n">
         <v>46216.35833333333</v>
       </c>
-      <c r="G253" s="3">
+      <c r="G253" s="5">
         <f>IF(AND(E253&lt;&gt;"",F253&lt;&gt;""),F253-E253,"")</f>
         <v/>
       </c>
@@ -12652,10 +12653,10 @@
           <t>Service interruption of 8 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Rawang 1, Batang Kali / Kuala Kubu Baru area, Selangor</t>
         </is>
       </c>
-      <c r="E254" s="2" t="n">
+      <c r="E254" s="4" t="n">
         <v>46216.35833333333</v>
       </c>
-      <c r="G254" s="3">
+      <c r="G254" s="5">
         <f>IF(AND(E254&lt;&gt;"",F254&lt;&gt;""),F254-E254,"")</f>
         <v/>
       </c>
@@ -12691,10 +12692,10 @@
           <t>Service interruption of 8 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Rawang 1, Batang Kali / Kuala Kubu Baru area, Selangor</t>
         </is>
       </c>
-      <c r="E255" s="2" t="n">
+      <c r="E255" s="4" t="n">
         <v>46216.35833333333</v>
       </c>
-      <c r="G255" s="3">
+      <c r="G255" s="5">
         <f>IF(AND(E255&lt;&gt;"",F255&lt;&gt;""),F255-E255,"")</f>
         <v/>
       </c>
@@ -12730,10 +12731,10 @@
           <t>Service interruption of 8 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Rawang 1, Batang Kali / Kuala Kubu Baru area, Selangor</t>
         </is>
       </c>
-      <c r="E256" s="2" t="n">
+      <c r="E256" s="4" t="n">
         <v>46216.35833333333</v>
       </c>
-      <c r="G256" s="3">
+      <c r="G256" s="5">
         <f>IF(AND(E256&lt;&gt;"",F256&lt;&gt;""),F256-E256,"")</f>
         <v/>
       </c>
@@ -12769,10 +12770,10 @@
           <t>Service interruption of 8 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Rawang 1, Batang Kali / Kuala Kubu Baru area, Selangor</t>
         </is>
       </c>
-      <c r="E257" s="2" t="n">
+      <c r="E257" s="4" t="n">
         <v>46216.35833333333</v>
       </c>
-      <c r="G257" s="3">
+      <c r="G257" s="5">
         <f>IF(AND(E257&lt;&gt;"",F257&lt;&gt;""),F257-E257,"")</f>
         <v/>
       </c>
@@ -12808,10 +12809,10 @@
           <t>Service interruption of 8 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Rawang 1, Batang Kali / Kuala Kubu Baru area, Selangor</t>
         </is>
       </c>
-      <c r="E258" s="2" t="n">
+      <c r="E258" s="4" t="n">
         <v>46216.35833333333</v>
       </c>
-      <c r="G258" s="3">
+      <c r="G258" s="5">
         <f>IF(AND(E258&lt;&gt;"",F258&lt;&gt;""),F258-E258,"")</f>
         <v/>
       </c>
@@ -12847,10 +12848,10 @@
           <t>Service interruption of 8 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Rawang 1, Batang Kali / Kuala Kubu Baru area, Selangor</t>
         </is>
       </c>
-      <c r="E259" s="2" t="n">
+      <c r="E259" s="4" t="n">
         <v>46216.35833333333</v>
       </c>
-      <c r="G259" s="3">
+      <c r="G259" s="5">
         <f>IF(AND(E259&lt;&gt;"",F259&lt;&gt;""),F259-E259,"")</f>
         <v/>
       </c>
@@ -12886,13 +12887,13 @@
           <t>Service interruption of 10 (2G)(4G) xD sites at certain parts of Matang / Petra, Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E260" s="2" t="n">
+      <c r="E260" s="4" t="n">
         <v>46216.23125</v>
       </c>
-      <c r="F260" s="2" t="n">
+      <c r="F260" s="4" t="n">
         <v>46216.68958333333</v>
       </c>
-      <c r="G260" s="3">
+      <c r="G260" s="5">
         <f>IF(AND(E260&lt;&gt;"",F260&lt;&gt;""),F260-E260,"")</f>
         <v/>
       </c>
@@ -12938,13 +12939,13 @@
           <t>Service interruption of 10 (2G)(4G) xD sites at certain parts of Matang / Petra, Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E261" s="2" t="n">
+      <c r="E261" s="4" t="n">
         <v>46216.23125</v>
       </c>
-      <c r="F261" s="2" t="n">
+      <c r="F261" s="4" t="n">
         <v>46216.68958333333</v>
       </c>
-      <c r="G261" s="3">
+      <c r="G261" s="5">
         <f>IF(AND(E261&lt;&gt;"",F261&lt;&gt;""),F261-E261,"")</f>
         <v/>
       </c>
@@ -12990,13 +12991,13 @@
           <t>Service interruption of 10 (2G)(4G) xD sites at certain parts of Matang / Petra, Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E262" s="2" t="n">
+      <c r="E262" s="4" t="n">
         <v>46216.23125</v>
       </c>
-      <c r="F262" s="2" t="n">
+      <c r="F262" s="4" t="n">
         <v>46216.68958333333</v>
       </c>
-      <c r="G262" s="3">
+      <c r="G262" s="5">
         <f>IF(AND(E262&lt;&gt;"",F262&lt;&gt;""),F262-E262,"")</f>
         <v/>
       </c>
@@ -13042,13 +13043,13 @@
           <t>Service interruption of 10 (2G)(4G) xD sites at certain parts of Matang / Petra, Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E263" s="2" t="n">
+      <c r="E263" s="4" t="n">
         <v>46216.23125</v>
       </c>
-      <c r="F263" s="2" t="n">
+      <c r="F263" s="4" t="n">
         <v>46216.68958333333</v>
       </c>
-      <c r="G263" s="3">
+      <c r="G263" s="5">
         <f>IF(AND(E263&lt;&gt;"",F263&lt;&gt;""),F263-E263,"")</f>
         <v/>
       </c>
@@ -13094,13 +13095,13 @@
           <t>Service interruption of 10 (2G)(4G) xD sites at certain parts of Matang / Petra, Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E264" s="2" t="n">
+      <c r="E264" s="4" t="n">
         <v>46216.23125</v>
       </c>
-      <c r="F264" s="2" t="n">
+      <c r="F264" s="4" t="n">
         <v>46216.68958333333</v>
       </c>
-      <c r="G264" s="3">
+      <c r="G264" s="5">
         <f>IF(AND(E264&lt;&gt;"",F264&lt;&gt;""),F264-E264,"")</f>
         <v/>
       </c>
@@ -13146,13 +13147,13 @@
           <t>Service interruption of 10 (2G)(4G) xD sites at certain parts of Matang / Petra, Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E265" s="2" t="n">
+      <c r="E265" s="4" t="n">
         <v>46216.23125</v>
       </c>
-      <c r="F265" s="2" t="n">
+      <c r="F265" s="4" t="n">
         <v>46216.68958333333</v>
       </c>
-      <c r="G265" s="3">
+      <c r="G265" s="5">
         <f>IF(AND(E265&lt;&gt;"",F265&lt;&gt;""),F265-E265,"")</f>
         <v/>
       </c>
@@ -13198,13 +13199,13 @@
           <t>Service interruption of 10 (2G)(4G) xD sites at certain parts of Matang / Petra, Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E266" s="2" t="n">
+      <c r="E266" s="4" t="n">
         <v>46216.23125</v>
       </c>
-      <c r="F266" s="2" t="n">
+      <c r="F266" s="4" t="n">
         <v>46216.68958333333</v>
       </c>
-      <c r="G266" s="3">
+      <c r="G266" s="5">
         <f>IF(AND(E266&lt;&gt;"",F266&lt;&gt;""),F266-E266,"")</f>
         <v/>
       </c>
@@ -13250,13 +13251,13 @@
           <t>Service interruption of 10 (2G)(4G) xD sites at certain parts of Matang / Petra, Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E267" s="2" t="n">
+      <c r="E267" s="4" t="n">
         <v>46216.23125</v>
       </c>
-      <c r="F267" s="2" t="n">
+      <c r="F267" s="4" t="n">
         <v>46216.68958333333</v>
       </c>
-      <c r="G267" s="3">
+      <c r="G267" s="5">
         <f>IF(AND(E267&lt;&gt;"",F267&lt;&gt;""),F267-E267,"")</f>
         <v/>
       </c>
@@ -13302,13 +13303,13 @@
           <t>Service interruption of 10 (2G)(4G) xD sites at certain parts of Matang / Petra, Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E268" s="2" t="n">
+      <c r="E268" s="4" t="n">
         <v>46216.23125</v>
       </c>
-      <c r="F268" s="2" t="n">
+      <c r="F268" s="4" t="n">
         <v>46216.68958333333</v>
       </c>
-      <c r="G268" s="3">
+      <c r="G268" s="5">
         <f>IF(AND(E268&lt;&gt;"",F268&lt;&gt;""),F268-E268,"")</f>
         <v/>
       </c>
@@ -13354,13 +13355,13 @@
           <t>Service interruption of 10 (2G)(4G) xD sites at certain parts of Matang / Petra, Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E269" s="2" t="n">
+      <c r="E269" s="4" t="n">
         <v>46216.23125</v>
       </c>
-      <c r="F269" s="2" t="n">
+      <c r="F269" s="4" t="n">
         <v>46216.68958333333</v>
       </c>
-      <c r="G269" s="3">
+      <c r="G269" s="5">
         <f>IF(AND(E269&lt;&gt;"",F269&lt;&gt;""),F269-E269,"")</f>
         <v/>
       </c>
@@ -13406,13 +13407,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E270" s="2" t="n">
+      <c r="E270" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F270" s="2" t="n">
+      <c r="F270" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G270" s="3">
+      <c r="G270" s="5">
         <f>IF(AND(E270&lt;&gt;"",F270&lt;&gt;""),F270-E270,"")</f>
         <v/>
       </c>
@@ -13458,13 +13459,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E271" s="2" t="n">
+      <c r="E271" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F271" s="2" t="n">
+      <c r="F271" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G271" s="3">
+      <c r="G271" s="5">
         <f>IF(AND(E271&lt;&gt;"",F271&lt;&gt;""),F271-E271,"")</f>
         <v/>
       </c>
@@ -13510,13 +13511,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E272" s="2" t="n">
+      <c r="E272" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F272" s="2" t="n">
+      <c r="F272" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G272" s="3">
+      <c r="G272" s="5">
         <f>IF(AND(E272&lt;&gt;"",F272&lt;&gt;""),F272-E272,"")</f>
         <v/>
       </c>
@@ -13562,13 +13563,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E273" s="2" t="n">
+      <c r="E273" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F273" s="2" t="n">
+      <c r="F273" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G273" s="3">
+      <c r="G273" s="5">
         <f>IF(AND(E273&lt;&gt;"",F273&lt;&gt;""),F273-E273,"")</f>
         <v/>
       </c>
@@ -13614,13 +13615,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E274" s="2" t="n">
+      <c r="E274" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F274" s="2" t="n">
+      <c r="F274" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G274" s="3">
+      <c r="G274" s="5">
         <f>IF(AND(E274&lt;&gt;"",F274&lt;&gt;""),F274-E274,"")</f>
         <v/>
       </c>
@@ -13666,13 +13667,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E275" s="2" t="n">
+      <c r="E275" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F275" s="2" t="n">
+      <c r="F275" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G275" s="3">
+      <c r="G275" s="5">
         <f>IF(AND(E275&lt;&gt;"",F275&lt;&gt;""),F275-E275,"")</f>
         <v/>
       </c>
@@ -13718,13 +13719,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E276" s="2" t="n">
+      <c r="E276" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F276" s="2" t="n">
+      <c r="F276" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G276" s="3">
+      <c r="G276" s="5">
         <f>IF(AND(E276&lt;&gt;"",F276&lt;&gt;""),F276-E276,"")</f>
         <v/>
       </c>
@@ -13770,13 +13771,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E277" s="2" t="n">
+      <c r="E277" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F277" s="2" t="n">
+      <c r="F277" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G277" s="3">
+      <c r="G277" s="5">
         <f>IF(AND(E277&lt;&gt;"",F277&lt;&gt;""),F277-E277,"")</f>
         <v/>
       </c>
@@ -13822,13 +13823,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E278" s="2" t="n">
+      <c r="E278" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F278" s="2" t="n">
+      <c r="F278" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G278" s="3">
+      <c r="G278" s="5">
         <f>IF(AND(E278&lt;&gt;"",F278&lt;&gt;""),F278-E278,"")</f>
         <v/>
       </c>
@@ -13874,13 +13875,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E279" s="2" t="n">
+      <c r="E279" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F279" s="2" t="n">
+      <c r="F279" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G279" s="3">
+      <c r="G279" s="5">
         <f>IF(AND(E279&lt;&gt;"",F279&lt;&gt;""),F279-E279,"")</f>
         <v/>
       </c>
@@ -13926,13 +13927,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E280" s="2" t="n">
+      <c r="E280" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F280" s="2" t="n">
+      <c r="F280" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G280" s="3">
+      <c r="G280" s="5">
         <f>IF(AND(E280&lt;&gt;"",F280&lt;&gt;""),F280-E280,"")</f>
         <v/>
       </c>
@@ -13978,13 +13979,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E281" s="2" t="n">
+      <c r="E281" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F281" s="2" t="n">
+      <c r="F281" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G281" s="3">
+      <c r="G281" s="5">
         <f>IF(AND(E281&lt;&gt;"",F281&lt;&gt;""),F281-E281,"")</f>
         <v/>
       </c>
@@ -14030,13 +14031,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E282" s="2" t="n">
+      <c r="E282" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F282" s="2" t="n">
+      <c r="F282" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G282" s="3">
+      <c r="G282" s="5">
         <f>IF(AND(E282&lt;&gt;"",F282&lt;&gt;""),F282-E282,"")</f>
         <v/>
       </c>
@@ -14082,13 +14083,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E283" s="2" t="n">
+      <c r="E283" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F283" s="2" t="n">
+      <c r="F283" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G283" s="3">
+      <c r="G283" s="5">
         <f>IF(AND(E283&lt;&gt;"",F283&lt;&gt;""),F283-E283,"")</f>
         <v/>
       </c>
@@ -14134,13 +14135,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E284" s="2" t="n">
+      <c r="E284" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F284" s="2" t="n">
+      <c r="F284" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G284" s="3">
+      <c r="G284" s="5">
         <f>IF(AND(E284&lt;&gt;"",F284&lt;&gt;""),F284-E284,"")</f>
         <v/>
       </c>
@@ -14186,13 +14187,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E285" s="2" t="n">
+      <c r="E285" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F285" s="2" t="n">
+      <c r="F285" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G285" s="3">
+      <c r="G285" s="5">
         <f>IF(AND(E285&lt;&gt;"",F285&lt;&gt;""),F285-E285,"")</f>
         <v/>
       </c>
@@ -14238,13 +14239,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E286" s="2" t="n">
+      <c r="E286" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F286" s="2" t="n">
+      <c r="F286" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G286" s="3">
+      <c r="G286" s="5">
         <f>IF(AND(E286&lt;&gt;"",F286&lt;&gt;""),F286-E286,"")</f>
         <v/>
       </c>
@@ -14290,13 +14291,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E287" s="2" t="n">
+      <c r="E287" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F287" s="2" t="n">
+      <c r="F287" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G287" s="3">
+      <c r="G287" s="5">
         <f>IF(AND(E287&lt;&gt;"",F287&lt;&gt;""),F287-E287,"")</f>
         <v/>
       </c>
@@ -14342,13 +14343,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E288" s="2" t="n">
+      <c r="E288" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F288" s="2" t="n">
+      <c r="F288" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G288" s="3">
+      <c r="G288" s="5">
         <f>IF(AND(E288&lt;&gt;"",F288&lt;&gt;""),F288-E288,"")</f>
         <v/>
       </c>
@@ -14394,13 +14395,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E289" s="2" t="n">
+      <c r="E289" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F289" s="2" t="n">
+      <c r="F289" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G289" s="3">
+      <c r="G289" s="5">
         <f>IF(AND(E289&lt;&gt;"",F289&lt;&gt;""),F289-E289,"")</f>
         <v/>
       </c>
@@ -14446,13 +14447,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E290" s="2" t="n">
+      <c r="E290" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F290" s="2" t="n">
+      <c r="F290" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G290" s="3">
+      <c r="G290" s="5">
         <f>IF(AND(E290&lt;&gt;"",F290&lt;&gt;""),F290-E290,"")</f>
         <v/>
       </c>
@@ -14498,13 +14499,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E291" s="2" t="n">
+      <c r="E291" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F291" s="2" t="n">
+      <c r="F291" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G291" s="3">
+      <c r="G291" s="5">
         <f>IF(AND(E291&lt;&gt;"",F291&lt;&gt;""),F291-E291,"")</f>
         <v/>
       </c>
@@ -14550,13 +14551,13 @@
           <t>Service interruption of 8 (2G)(4G) xD and 15 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi area, Sarawak</t>
         </is>
       </c>
-      <c r="E292" s="2" t="n">
+      <c r="E292" s="4" t="n">
         <v>46216.03819444445</v>
       </c>
-      <c r="F292" s="2" t="n">
+      <c r="F292" s="4" t="n">
         <v>46216.05694444444</v>
       </c>
-      <c r="G292" s="3">
+      <c r="G292" s="5">
         <f>IF(AND(E292&lt;&gt;"",F292&lt;&gt;""),F292-E292,"")</f>
         <v/>
       </c>
